--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/ratio.alpha.natif/RANDOMSEARCH_DETAILS_ratio.alpha.natif.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/ratio.alpha.natif/RANDOMSEARCH_DETAILS_ratio.alpha.natif.xlsx
@@ -469,17 +469,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9674</v>
+        <v>0.9676</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0476</v>
+        <v>0.0479</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.1019</v>
       </c>
     </row>
     <row r="3">
@@ -498,17 +498,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9746</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0462</v>
+        <v>0.0387</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4">
@@ -527,17 +527,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9016</v>
+        <v>0.9012</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0613</v>
+        <v>0.0614</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.1121</v>
       </c>
     </row>
     <row r="5">
@@ -556,17 +556,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8264</v>
+        <v>0.8262</v>
       </c>
       <c r="F5" t="n">
         <v>0.07240000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.1121</v>
       </c>
     </row>
     <row r="6">
@@ -585,17 +585,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8284</v>
+        <v>0.8286</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0722</v>
+        <v>0.0721</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.1125</v>
       </c>
     </row>
     <row r="7">
@@ -614,17 +614,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8534</v>
+        <v>0.8538</v>
       </c>
       <c r="F7" t="n">
         <v>0.0746</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.1176</v>
       </c>
     </row>
     <row r="8">
@@ -643,17 +643,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9684</v>
+        <v>0.9702</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0446</v>
+        <v>0.0442</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.1065</v>
       </c>
     </row>
     <row r="9">
@@ -672,17 +672,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9774</v>
+        <v>0.9775</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0428</v>
+        <v>0.0427</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.1007</v>
       </c>
     </row>
     <row r="10">
@@ -701,17 +701,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.922</v>
+        <v>0.9223</v>
       </c>
       <c r="F10" t="n">
         <v>0.0584</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.1061</v>
       </c>
     </row>
     <row r="11">
@@ -730,17 +730,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9152</v>
+        <v>0.9151</v>
       </c>
       <c r="F11" t="n">
         <v>0.0589</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.1046</v>
       </c>
     </row>
     <row r="12">
@@ -759,17 +759,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9142</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="F12" t="n">
         <v>0.0591</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.1059</v>
       </c>
     </row>
     <row r="13">
@@ -788,17 +788,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9634</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="F13" t="n">
         <v>0.0442</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.1057</v>
       </c>
     </row>
     <row r="14">
@@ -817,7 +817,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -827,7 +827,7 @@
         <v>0.0595</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.1057</v>
       </c>
     </row>
     <row r="15">
@@ -846,7 +846,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -856,7 +856,7 @@
         <v>0.0594</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.1055</v>
       </c>
     </row>
     <row r="16">
@@ -875,7 +875,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -885,7 +885,7 @@
         <v>0.0589</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.1047</v>
       </c>
     </row>
     <row r="17">
@@ -904,17 +904,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9142</v>
+        <v>0.9137</v>
       </c>
       <c r="F17" t="n">
         <v>0.0589</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.1054</v>
       </c>
     </row>
     <row r="18">
@@ -933,17 +933,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9857</v>
+        <v>0.9801</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0399</v>
+        <v>0.0407</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.1082</v>
       </c>
     </row>
     <row r="19">
@@ -962,17 +962,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9609</v>
+        <v>0.9611</v>
       </c>
       <c r="F19" t="n">
         <v>0.0541</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.1065</v>
       </c>
     </row>
     <row r="20">
@@ -991,7 +991,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1001,7 +1001,7 @@
         <v>0.0424</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.1062</v>
       </c>
     </row>
     <row r="21">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9812</v>
+        <v>0.9549</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0392</v>
+        <v>0.055</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.1074</v>
       </c>
     </row>
     <row r="22">
@@ -1049,17 +1049,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9345</v>
+        <v>0.9351</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0579</v>
+        <v>0.0577</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.1081</v>
       </c>
     </row>
     <row r="23">
@@ -1078,17 +1078,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9736</v>
+        <v>0.9728</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0444</v>
+        <v>0.0446</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.1082</v>
       </c>
     </row>
     <row r="24">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9376</v>
+        <v>0.9384</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0586</v>
+        <v>0.0585</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.1083</v>
       </c>
     </row>
     <row r="25">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1146,7 +1146,7 @@
         <v>0.0478</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="26">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9813</v>
+        <v>0.9811</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0414</v>
+        <v>0.0415</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.1083</v>
       </c>
     </row>
     <row r="27">
@@ -1194,17 +1194,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9831</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0407</v>
+        <v>0.0408</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.1085</v>
       </c>
     </row>
     <row r="28">
@@ -1223,17 +1223,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>0.9585</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0568</v>
+        <v>0.0569</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.1087</v>
       </c>
     </row>
     <row r="29">
@@ -1252,17 +1252,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9664</v>
+        <v>0.9665</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0528</v>
+        <v>0.0529</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.1053</v>
       </c>
     </row>
     <row r="30">
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9809</v>
+        <v>0.9808</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0429</v>
+        <v>0.0428</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.1058</v>
       </c>
     </row>
     <row r="31">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9817</v>
+        <v>0.9816</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0399</v>
+        <v>0.04</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.1077</v>
       </c>
     </row>
     <row r="32">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9731</v>
+        <v>0.98</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0443</v>
+        <v>0.0396</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.1073</v>
       </c>
     </row>
     <row r="33">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9774</v>
+        <v>0.9779</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0425</v>
+        <v>0.0432</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.1063</v>
       </c>
     </row>
     <row r="34">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9701</v>
+        <v>0.9699</v>
       </c>
       <c r="F34" t="n">
         <v>0.0471</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.1028</v>
       </c>
     </row>
     <row r="35">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9819</v>
+        <v>0.9866</v>
       </c>
       <c r="F35" t="n">
-        <v>0.038</v>
+        <v>0.0368</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.1009</v>
       </c>
     </row>
     <row r="36">
@@ -1455,17 +1455,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9847</v>
+        <v>0.9815</v>
       </c>
       <c r="F36" t="n">
-        <v>0.04</v>
+        <v>0.0416</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.1011</v>
       </c>
     </row>
     <row r="37">
@@ -1484,17 +1484,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.964</v>
+        <v>0.9807</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0453</v>
+        <v>0.0352</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.0978</v>
       </c>
     </row>
     <row r="38">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9651</v>
+        <v>0.9645</v>
       </c>
       <c r="F38" t="n">
         <v>0.0443</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.0963</v>
       </c>
     </row>
     <row r="39">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9742</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0391</v>
+        <v>0.039</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.0978</v>
       </c>
     </row>
     <row r="40">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9706</v>
+        <v>0.9758</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0422</v>
+        <v>0.0418</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.0994</v>
       </c>
     </row>
     <row r="41">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9701</v>
+        <v>0.97</v>
       </c>
       <c r="F41" t="n">
         <v>0.047</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.1027</v>
       </c>
     </row>
     <row r="42">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9822</v>
+        <v>0.9813</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0379</v>
+        <v>0.0382</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.1005</v>
       </c>
     </row>
     <row r="43">
@@ -1658,17 +1658,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9845</v>
+        <v>0.9821</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0401</v>
+        <v>0.0416</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="44">
@@ -1687,17 +1687,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.979</v>
+        <v>0.9806</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0373</v>
+        <v>0.035</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.0968</v>
       </c>
     </row>
     <row r="45">
@@ -1716,17 +1716,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9641</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0364</v>
+        <v>0.0446</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>0.0964</v>
       </c>
     </row>
     <row r="46">
@@ -1745,17 +1745,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9769</v>
+        <v>0.9776</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0378</v>
+        <v>0.0377</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="47">
@@ -1774,17 +1774,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9701</v>
+        <v>0.9705</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0428</v>
+        <v>0.0425</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.0988</v>
       </c>
     </row>
     <row r="48">
@@ -1803,17 +1803,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9818</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0404</v>
+        <v>0.0405</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.1005</v>
       </c>
     </row>
     <row r="49">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9556</v>
       </c>
       <c r="F49" t="n">
-        <v>0.037</v>
+        <v>0.0524</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="50">
@@ -1861,17 +1861,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.979</v>
+        <v>0.9792</v>
       </c>
       <c r="F50" t="n">
         <v>0.0469</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>0.1079</v>
       </c>
     </row>
     <row r="51">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.9104</v>
+        <v>0.9105</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0655</v>
+        <v>0.0654</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>0.1137</v>
       </c>
     </row>
     <row r="52">
@@ -1919,17 +1919,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.9267</v>
+        <v>0.9262</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0645</v>
+        <v>0.0646</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>0.1127</v>
       </c>
     </row>
     <row r="53">
@@ -1948,17 +1948,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9596</v>
+        <v>0.9599</v>
       </c>
       <c r="F53" t="n">
         <v>0.057</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>0.1099</v>
       </c>
     </row>
     <row r="54">
@@ -1977,17 +1977,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.9489</v>
+        <v>0.949</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0565</v>
+        <v>0.0566</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>0.1086</v>
       </c>
     </row>
     <row r="55">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0444</v>
+        <v>0.0397</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>0.1042</v>
       </c>
     </row>
     <row r="56">
@@ -2035,17 +2035,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9805</v>
+        <v>0.9804</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0414</v>
+        <v>0.0413</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>0.1061</v>
       </c>
     </row>
     <row r="57">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9822</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0459</v>
+        <v>0.0387</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>0.1083</v>
       </c>
     </row>
     <row r="58">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8294</v>
+        <v>0.8293</v>
       </c>
       <c r="F58" t="n">
         <v>0.0722</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>0.1127</v>
       </c>
     </row>
     <row r="59">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2132,7 +2132,7 @@
         <v>0.0722</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>0.1127</v>
       </c>
     </row>
     <row r="60">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.8682</v>
+        <v>0.8677</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0658</v>
+        <v>0.0659</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>0.1125</v>
       </c>
     </row>
     <row r="61">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.9349</v>
       </c>
       <c r="F61" t="n">
-        <v>0.066</v>
+        <v>0.0521</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>0.1126</v>
       </c>
     </row>
     <row r="62">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.9226</v>
+        <v>0.9227</v>
       </c>
       <c r="F62" t="n">
         <v>0.0607</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>0.1077</v>
       </c>
     </row>
     <row r="63">
@@ -2238,17 +2238,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.9648</v>
+        <v>0.9637</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0456</v>
+        <v>0.0457</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>0.1064</v>
       </c>
     </row>
     <row r="64">
@@ -2267,17 +2267,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.9179</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="F64" t="n">
         <v>0.0614</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>0.1079</v>
       </c>
     </row>
     <row r="65">
@@ -2296,17 +2296,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.9549</v>
+        <v>0.9553</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0483</v>
+        <v>0.0482</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>0.1076</v>
       </c>
     </row>
     <row r="66">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9779</v>
+        <v>0.9774</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0467</v>
+        <v>0.0468</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>0.1092</v>
       </c>
     </row>
     <row r="67">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9764</v>
+        <v>0.977</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0447</v>
+        <v>0.0445</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>0.1072</v>
       </c>
     </row>
     <row r="68">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9802</v>
+        <v>0.9809</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0417</v>
+        <v>0.0395</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>0.1074</v>
       </c>
     </row>
     <row r="69">
@@ -2412,17 +2412,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9518</v>
+        <v>0.9735</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0522</v>
+        <v>0.0424</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>0.1051</v>
       </c>
     </row>
     <row r="70">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9426</v>
+        <v>0.9735</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0533</v>
+        <v>0.0386</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="71">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9798</v>
+        <v>0.9797</v>
       </c>
       <c r="F71" t="n">
         <v>0.0416</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>0.1041</v>
       </c>
     </row>
     <row r="72">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9739</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0421</v>
+        <v>0.042</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>0.1063</v>
       </c>
     </row>
     <row r="73">
@@ -2528,17 +2528,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.971</v>
+        <v>0.972</v>
       </c>
       <c r="F73" t="n">
         <v>0.045</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>0.1042</v>
       </c>
     </row>
     <row r="74">
@@ -2557,17 +2557,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9656</v>
+        <v>0.9658</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0497</v>
+        <v>0.0495</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>0.1018</v>
       </c>
     </row>
     <row r="75">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9001</v>
+        <v>0.9004</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0646</v>
+        <v>0.0645</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>0.1107</v>
       </c>
     </row>
     <row r="76">
@@ -2615,17 +2615,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9001</v>
+        <v>0.9004</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0646</v>
+        <v>0.0645</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>0.1107</v>
       </c>
     </row>
     <row r="77">
@@ -2644,17 +2644,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8229</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0736</v>
+        <v>0.0735</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>0.1135</v>
       </c>
     </row>
     <row r="78">
@@ -2673,17 +2673,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8223</v>
+        <v>0.8224</v>
       </c>
       <c r="F78" t="n">
         <v>0.0735</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>0.1138</v>
       </c>
     </row>
     <row r="79">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2712,7 +2712,7 @@
         <v>0.0736</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>0.1138</v>
       </c>
     </row>
     <row r="80">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E80" t="n">
         <v>0.8226</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0735</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>0.1138</v>
       </c>
     </row>
     <row r="81">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.9755</v>
+        <v>0.9741</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0394</v>
+        <v>0.0425</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>0.1081</v>
       </c>
     </row>
     <row r="82">
@@ -2789,17 +2789,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E82" t="n">
         <v>0.9712</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0427</v>
+        <v>0.0426</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="83">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9091</v>
+        <v>0.8912</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0613</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>0.1106</v>
       </c>
     </row>
     <row r="84">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9084</v>
+        <v>0.8923</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0613</v>
+        <v>0.0649</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>0.1106</v>
       </c>
     </row>
     <row r="85">
@@ -2876,17 +2876,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E85" t="n">
         <v>0.8537</v>
       </c>
       <c r="F85" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0723</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>0.1108</v>
       </c>
     </row>
     <row r="86">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E86" t="n">
         <v>0.9324</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0641</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>0.1092</v>
       </c>
     </row>
     <row r="87">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9788</v>
+        <v>0.9791</v>
       </c>
       <c r="F87" t="n">
-        <v>0.0436</v>
+        <v>0.0435</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.1086</v>
       </c>
     </row>
     <row r="88">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9606</v>
+        <v>0.9609</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0531</v>
+        <v>0.053</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.1056</v>
       </c>
     </row>
     <row r="89">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9787</v>
+        <v>0.979</v>
       </c>
       <c r="F89" t="n">
         <v>0.0425</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="90">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -3031,7 +3031,7 @@
         <v>0.0415</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="91">
@@ -3050,17 +3050,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.979</v>
+        <v>0.9804</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0373</v>
+        <v>0.035</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="92">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9606</v>
+        <v>0.9609</v>
       </c>
       <c r="F92" t="n">
         <v>0.0531</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>0.1056</v>
       </c>
     </row>
     <row r="93">
@@ -3108,17 +3108,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.979</v>
+        <v>0.9804</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0373</v>
+        <v>0.035</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="94">
@@ -3137,17 +3137,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9016</v>
+        <v>0.9012</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0613</v>
+        <v>0.0614</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>0.1121</v>
       </c>
     </row>
     <row r="95">
@@ -3166,17 +3166,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.8579</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0722</v>
+        <v>0.0721</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>0.1196</v>
       </c>
     </row>
     <row r="96">
@@ -3195,17 +3195,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.8948</v>
+        <v>0.8954</v>
       </c>
       <c r="F96" t="n">
         <v>0.0626</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>0.1123</v>
       </c>
     </row>
     <row r="97">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.8933</v>
+        <v>0.8859</v>
       </c>
       <c r="F97" t="n">
-        <v>0.063</v>
+        <v>0.0636</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>0.1123</v>
       </c>
     </row>
     <row r="98">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -3263,7 +3263,7 @@
         <v>0.0435</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="99">
@@ -3282,17 +3282,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9779</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0424</v>
+        <v>0.0436</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>0.1093</v>
       </c>
     </row>
     <row r="100">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9705</v>
+        <v>0.9709</v>
       </c>
       <c r="F100" t="n">
-        <v>0.0471</v>
+        <v>0.0468</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>0.1089</v>
       </c>
     </row>
     <row r="101">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9746</v>
+        <v>0.9755</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0412</v>
+        <v>0.0409</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>0.1084</v>
       </c>
     </row>
     <row r="102">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.965</v>
       </c>
       <c r="F102" t="n">
-        <v>0.0415</v>
+        <v>0.0474</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>0.1097</v>
       </c>
     </row>
     <row r="103">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9822</v>
+        <v>0.9823</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0472</v>
+        <v>0.0473</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="104">
@@ -3427,17 +3427,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9835</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0395</v>
+        <v>0.0399</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="105">
@@ -3456,17 +3456,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9815</v>
+        <v>0.9818</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0437</v>
+        <v>0.0436</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>0.1092</v>
       </c>
     </row>
     <row r="106">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9808</v>
+        <v>0.9754</v>
       </c>
       <c r="F106" t="n">
-        <v>0.0406</v>
+        <v>0.0466</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>0.1094</v>
       </c>
     </row>
     <row r="107">
@@ -3514,17 +3514,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9449</v>
+        <v>0.9444</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0569</v>
+        <v>0.0564</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="108">
@@ -3543,17 +3543,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9893</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0402</v>
+        <v>0.0404</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="109">
@@ -3572,17 +3572,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9909</v>
+        <v>0.9858</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0369</v>
+        <v>0.0425</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="110">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9781</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0373</v>
+        <v>0.04</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>0.0982</v>
       </c>
     </row>
     <row r="111">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9835</v>
+        <v>0.9833</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0359</v>
+        <v>0.0361</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>0.09619999999999999</v>
       </c>
     </row>
     <row r="112">
@@ -3659,17 +3659,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9889</v>
+        <v>0.9811</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0402</v>
+        <v>0.0447</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>0.1029</v>
       </c>
     </row>
     <row r="113">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9623</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="F113" t="n">
         <v>0.0544</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>0.1017</v>
       </c>
     </row>
     <row r="114">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9705</v>
+        <v>0.9794</v>
       </c>
       <c r="F114" t="n">
-        <v>0.047</v>
+        <v>0.0393</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>0.0974</v>
       </c>
     </row>
     <row r="115">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9838</v>
+        <v>0.9841</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0362</v>
+        <v>0.036</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>0.0963</v>
       </c>
     </row>
     <row r="116">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9751</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0412</v>
+        <v>0.0409</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>0.1083</v>
       </c>
     </row>
     <row r="117">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -3814,7 +3814,7 @@
         <v>0.0577</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>0.1095</v>
       </c>
     </row>
     <row r="118">
@@ -3833,17 +3833,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9815</v>
+        <v>0.9818</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0437</v>
+        <v>0.0436</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>0.1092</v>
       </c>
     </row>
     <row r="119">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9623</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="F119" t="n">
         <v>0.0544</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>0.1017</v>
       </c>
     </row>
     <row r="120">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9295</v>
+        <v>0.9297</v>
       </c>
       <c r="F120" t="n">
         <v>0.0617</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>0.1128</v>
       </c>
     </row>
     <row r="121">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9295</v>
+        <v>0.9297</v>
       </c>
       <c r="F121" t="n">
         <v>0.0617</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>0.1128</v>
       </c>
     </row>
     <row r="122">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9778</v>
+        <v>0.9784</v>
       </c>
       <c r="F122" t="n">
         <v>0.0424</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>0.1104</v>
       </c>
     </row>
     <row r="123">
@@ -3978,17 +3978,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9627</v>
+        <v>0.9826</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0544</v>
+        <v>0.0382</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>0.1016</v>
       </c>
     </row>
     <row r="124">
@@ -4007,17 +4007,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9835</v>
+        <v>0.9777</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0381</v>
+        <v>0.0398</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="125">
@@ -4036,17 +4036,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9022</v>
+        <v>0.9021</v>
       </c>
       <c r="F125" t="n">
         <v>0.0612</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>0.1119</v>
       </c>
     </row>
     <row r="126">
@@ -4065,17 +4065,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9811</v>
+        <v>0.9686</v>
       </c>
       <c r="F126" t="n">
-        <v>0.0397</v>
+        <v>0.047</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>0.1091</v>
       </c>
     </row>
     <row r="127">
@@ -4094,17 +4094,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.8946</v>
+        <v>0.8939</v>
       </c>
       <c r="F127" t="n">
         <v>0.06270000000000001</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>0.1131</v>
       </c>
     </row>
     <row r="128">
@@ -4123,17 +4123,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.9699</v>
+        <v>0.959</v>
       </c>
       <c r="F128" t="n">
-        <v>0.0441</v>
+        <v>0.0469</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>0.1075</v>
       </c>
     </row>
     <row r="129">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.9685</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0444</v>
+        <v>0.0442</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>0.1081</v>
       </c>
     </row>
     <row r="130">
@@ -4181,17 +4181,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.9669</v>
+        <v>0.9665</v>
       </c>
       <c r="F130" t="n">
-        <v>0.047</v>
+        <v>0.0471</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>0.1085</v>
       </c>
     </row>
     <row r="131">
@@ -4210,17 +4210,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.9651</v>
+        <v>0.9668</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0451</v>
+        <v>0.0467</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>0.1085</v>
       </c>
     </row>
     <row r="132">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.9726</v>
+        <v>0.9585</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0446</v>
+        <v>0.0478</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="133">
@@ -4268,17 +4268,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.9717</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0446</v>
+        <v>0.0447</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>0.1081</v>
       </c>
     </row>
     <row r="134">
@@ -4297,17 +4297,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.9696</v>
+        <v>0.966</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0417</v>
+        <v>0.0469</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>0.1082</v>
       </c>
     </row>
     <row r="135">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -4336,7 +4336,7 @@
         <v>0.05</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="136">
@@ -4355,17 +4355,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.9704</v>
+        <v>0.9666</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0412</v>
+        <v>0.0464</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>0.1087</v>
       </c>
     </row>
     <row r="137">
@@ -4384,17 +4384,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9823</v>
+        <v>0.9821</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0435</v>
+        <v>0.0436</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>0.1087</v>
       </c>
     </row>
     <row r="138">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9621</v>
       </c>
       <c r="F138" t="n">
-        <v>0.0401</v>
+        <v>0.0539</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="139">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -4452,7 +4452,7 @@
         <v>0.0442</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>0.1108</v>
       </c>
     </row>
     <row r="140">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.9888</v>
+        <v>0.9879</v>
       </c>
       <c r="F140" t="n">
-        <v>0.0385</v>
+        <v>0.0386</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>0.1034</v>
       </c>
     </row>
     <row r="141">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9863</v>
+        <v>0.9869</v>
       </c>
       <c r="F141" t="n">
-        <v>0.0357</v>
+        <v>0.0359</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>0.1011</v>
       </c>
     </row>
     <row r="142">
@@ -4529,17 +4529,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9621</v>
       </c>
       <c r="F142" t="n">
-        <v>0.0401</v>
+        <v>0.0539</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="143">
@@ -4558,17 +4558,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9648</v>
       </c>
       <c r="F143" t="n">
-        <v>0.0572</v>
+        <v>0.0573</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>0.1132</v>
       </c>
     </row>
     <row r="144">
@@ -4587,17 +4587,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9604</v>
+        <v>0.9606</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0578</v>
+        <v>0.0579</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>0.1122</v>
       </c>
     </row>
     <row r="145">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9863</v>
+        <v>0.9869</v>
       </c>
       <c r="F145" t="n">
-        <v>0.0357</v>
+        <v>0.0359</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>0.1011</v>
       </c>
     </row>
     <row r="146">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.8949</v>
+        <v>0.8943</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0623</v>
+        <v>0.0624</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>0.1136</v>
       </c>
     </row>
     <row r="147">
@@ -4674,17 +4674,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E147" t="n">
         <v>0.8932</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0625</v>
+        <v>0.0626</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>0.1135</v>
       </c>
     </row>
     <row r="148">
@@ -4703,17 +4703,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.8889</v>
+        <v>0.8884</v>
       </c>
       <c r="F148" t="n">
         <v>0.0629</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>0.1136</v>
       </c>
     </row>
     <row r="149">
@@ -4732,17 +4732,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.8864</v>
+        <v>0.8892</v>
       </c>
       <c r="F149" t="n">
-        <v>0.0634</v>
+        <v>0.063</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>0.1138</v>
       </c>
     </row>
     <row r="150">
@@ -4761,17 +4761,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.8924</v>
+        <v>0.8917</v>
       </c>
       <c r="F150" t="n">
-        <v>0.0631</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>0.1131</v>
       </c>
     </row>
     <row r="151">
@@ -4790,17 +4790,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.8932</v>
+        <v>0.8923</v>
       </c>
       <c r="F151" t="n">
-        <v>0.0629</v>
+        <v>0.063</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>0.1136</v>
       </c>
     </row>
     <row r="152">
@@ -4819,17 +4819,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.8935999999999999</v>
+        <v>0.8929</v>
       </c>
       <c r="F152" t="n">
         <v>0.06279999999999999</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>0.1138</v>
       </c>
     </row>
     <row r="153">
@@ -4848,17 +4848,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.8958</v>
+        <v>0.8778</v>
       </c>
       <c r="F153" t="n">
-        <v>0.0625</v>
+        <v>0.0665</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="154">
@@ -4877,17 +4877,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.8884</v>
+        <v>0.8919</v>
       </c>
       <c r="F154" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0629</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="155">
@@ -4906,17 +4906,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.9325</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="F155" t="n">
         <v>0.0569</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="156">
@@ -4935,17 +4935,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9584</v>
       </c>
       <c r="F156" t="n">
-        <v>0.047</v>
+        <v>0.0471</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>0.1107</v>
       </c>
     </row>
     <row r="157">
@@ -4964,17 +4964,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.9212</v>
+        <v>0.9204</v>
       </c>
       <c r="F157" t="n">
-        <v>0.0593</v>
+        <v>0.0595</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>0.1112</v>
       </c>
     </row>
     <row r="158">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.9547</v>
+        <v>0.9565</v>
       </c>
       <c r="F158" t="n">
         <v>0.0537</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>0.1126</v>
       </c>
     </row>
     <row r="159">
@@ -5022,17 +5022,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.9207</v>
+        <v>0.9115</v>
       </c>
       <c r="F159" t="n">
         <v>0.063</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>0.1109</v>
       </c>
     </row>
     <row r="160">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.8521</v>
+        <v>0.8216</v>
       </c>
       <c r="F160" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0751</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>0.1157</v>
       </c>
     </row>
     <row r="161">
@@ -5080,17 +5080,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.865</v>
+        <v>0.8659</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0688</v>
+        <v>0.0687</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>0.1153</v>
       </c>
     </row>
     <row r="162">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.9747</v>
+        <v>0.9655</v>
       </c>
       <c r="F162" t="n">
-        <v>0.0414</v>
+        <v>0.0491</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>0.1115</v>
       </c>
     </row>
     <row r="163">
@@ -5138,17 +5138,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.982</v>
+        <v>0.9818</v>
       </c>
       <c r="F163" t="n">
-        <v>0.0432</v>
+        <v>0.0431</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>0.1079</v>
       </c>
     </row>
     <row r="164">
@@ -5167,17 +5167,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.989</v>
+        <v>0.9881</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0385</v>
+        <v>0.0386</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>0.1034</v>
       </c>
     </row>
     <row r="165">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9022</v>
+        <v>0.9021</v>
       </c>
       <c r="F165" t="n">
         <v>0.0612</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>0.1119</v>
       </c>
     </row>
     <row r="166">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.8547</v>
+        <v>0.8536</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0726</v>
+        <v>0.0727</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>0.1196</v>
       </c>
     </row>
     <row r="167">
@@ -5254,17 +5254,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.964</v>
+        <v>0.9641</v>
       </c>
       <c r="F167" t="n">
         <v>0.0512</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>0.1037</v>
       </c>
     </row>
     <row r="168">
@@ -5283,17 +5283,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9857</v>
+        <v>0.9846</v>
       </c>
       <c r="F168" t="n">
-        <v>0.0381</v>
+        <v>0.0385</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>0.1027</v>
       </c>
     </row>
     <row r="169">
@@ -5312,17 +5312,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9741</v>
+        <v>0.98</v>
       </c>
       <c r="F169" t="n">
-        <v>0.0425</v>
+        <v>0.0394</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>0.1015</v>
       </c>
     </row>
     <row r="170">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.9827</v>
+        <v>0.982</v>
       </c>
       <c r="F170" t="n">
-        <v>0.038</v>
+        <v>0.0382</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>0.1019</v>
       </c>
     </row>
     <row r="171">
@@ -5370,17 +5370,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E171" t="n">
         <v>0.9815</v>
       </c>
       <c r="F171" t="n">
-        <v>0.0381</v>
+        <v>0.0382</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>0.0989</v>
       </c>
     </row>
     <row r="172">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9409</v>
+        <v>0.9338</v>
       </c>
       <c r="F172" t="n">
         <v>0.062</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>0.1127</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/ratio.alpha.natif/RANDOMSEARCH_DETAILS_ratio.alpha.natif.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/ratio.alpha.natif/RANDOMSEARCH_DETAILS_ratio.alpha.natif.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,10 +444,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>RMSEC</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>RMSECV</t>
         </is>
@@ -476,9 +481,12 @@
         <v>0.9676</v>
       </c>
       <c r="F2" t="n">
+        <v>1.8183</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.0479</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>0.1019</v>
       </c>
     </row>
@@ -505,9 +513,12 @@
         <v>0.9844000000000001</v>
       </c>
       <c r="F3" t="n">
+        <v>1.7881</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.0387</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -534,9 +545,12 @@
         <v>0.9012</v>
       </c>
       <c r="F4" t="n">
+        <v>1.9911</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.0614</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>0.1121</v>
       </c>
     </row>
@@ -563,9 +577,12 @@
         <v>0.8262</v>
       </c>
       <c r="F5" t="n">
+        <v>1.9908</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.07240000000000001</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>0.1121</v>
       </c>
     </row>
@@ -592,9 +609,12 @@
         <v>0.8286</v>
       </c>
       <c r="F6" t="n">
+        <v>1.9986</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.0721</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0.1125</v>
       </c>
     </row>
@@ -621,9 +641,12 @@
         <v>0.8538</v>
       </c>
       <c r="F7" t="n">
+        <v>2.0911</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.0746</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>0.1176</v>
       </c>
     </row>
@@ -650,9 +673,12 @@
         <v>0.9702</v>
       </c>
       <c r="F8" t="n">
+        <v>1.8937</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.0442</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>0.1065</v>
       </c>
     </row>
@@ -679,9 +705,12 @@
         <v>0.9775</v>
       </c>
       <c r="F9" t="n">
+        <v>1.799</v>
+      </c>
+      <c r="G9" t="n">
         <v>0.0427</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>0.1007</v>
       </c>
     </row>
@@ -708,9 +737,12 @@
         <v>0.9223</v>
       </c>
       <c r="F10" t="n">
+        <v>1.8883</v>
+      </c>
+      <c r="G10" t="n">
         <v>0.0584</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>0.1061</v>
       </c>
     </row>
@@ -737,9 +769,12 @@
         <v>0.9151</v>
       </c>
       <c r="F11" t="n">
+        <v>1.8624</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.0589</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>0.1046</v>
       </c>
     </row>
@@ -766,9 +801,12 @@
         <v>0.9137999999999999</v>
       </c>
       <c r="F12" t="n">
+        <v>1.8834</v>
+      </c>
+      <c r="G12" t="n">
         <v>0.0591</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>0.1059</v>
       </c>
     </row>
@@ -795,9 +833,12 @@
         <v>0.9631999999999999</v>
       </c>
       <c r="F13" t="n">
+        <v>1.8805</v>
+      </c>
+      <c r="G13" t="n">
         <v>0.0442</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>0.1057</v>
       </c>
     </row>
@@ -824,9 +865,12 @@
         <v>0.9137999999999999</v>
       </c>
       <c r="F14" t="n">
+        <v>1.8803</v>
+      </c>
+      <c r="G14" t="n">
         <v>0.0595</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>0.1057</v>
       </c>
     </row>
@@ -853,9 +897,12 @@
         <v>0.9144</v>
       </c>
       <c r="F15" t="n">
+        <v>1.8781</v>
+      </c>
+      <c r="G15" t="n">
         <v>0.0594</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>0.1055</v>
       </c>
     </row>
@@ -882,9 +929,12 @@
         <v>0.9149</v>
       </c>
       <c r="F16" t="n">
+        <v>1.8636</v>
+      </c>
+      <c r="G16" t="n">
         <v>0.0589</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>0.1047</v>
       </c>
     </row>
@@ -911,9 +961,12 @@
         <v>0.9137</v>
       </c>
       <c r="F17" t="n">
+        <v>1.8753</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.0589</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>0.1054</v>
       </c>
     </row>
@@ -940,9 +993,12 @@
         <v>0.9801</v>
       </c>
       <c r="F18" t="n">
+        <v>1.9231</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.0407</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>0.1082</v>
       </c>
     </row>
@@ -969,9 +1025,12 @@
         <v>0.9611</v>
       </c>
       <c r="F19" t="n">
+        <v>1.8943</v>
+      </c>
+      <c r="G19" t="n">
         <v>0.0541</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>0.1065</v>
       </c>
     </row>
@@ -998,9 +1057,12 @@
         <v>0.9815</v>
       </c>
       <c r="F20" t="n">
+        <v>1.8895</v>
+      </c>
+      <c r="G20" t="n">
         <v>0.0424</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>0.1062</v>
       </c>
     </row>
@@ -1027,9 +1089,12 @@
         <v>0.9549</v>
       </c>
       <c r="F21" t="n">
+        <v>1.9098</v>
+      </c>
+      <c r="G21" t="n">
         <v>0.055</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>0.1074</v>
       </c>
     </row>
@@ -1056,9 +1121,12 @@
         <v>0.9351</v>
       </c>
       <c r="F22" t="n">
+        <v>1.9208</v>
+      </c>
+      <c r="G22" t="n">
         <v>0.0577</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>0.1081</v>
       </c>
     </row>
@@ -1085,9 +1153,12 @@
         <v>0.9728</v>
       </c>
       <c r="F23" t="n">
+        <v>1.9228</v>
+      </c>
+      <c r="G23" t="n">
         <v>0.0446</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>0.1082</v>
       </c>
     </row>
@@ -1114,9 +1185,12 @@
         <v>0.9384</v>
       </c>
       <c r="F24" t="n">
+        <v>1.924</v>
+      </c>
+      <c r="G24" t="n">
         <v>0.0585</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>0.1083</v>
       </c>
     </row>
@@ -1143,9 +1217,12 @@
         <v>0.9649</v>
       </c>
       <c r="F25" t="n">
+        <v>1.9376</v>
+      </c>
+      <c r="G25" t="n">
         <v>0.0478</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>0.109</v>
       </c>
     </row>
@@ -1172,9 +1249,12 @@
         <v>0.9811</v>
       </c>
       <c r="F26" t="n">
+        <v>1.9245</v>
+      </c>
+      <c r="G26" t="n">
         <v>0.0415</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>0.1083</v>
       </c>
     </row>
@@ -1201,9 +1281,12 @@
         <v>0.9831</v>
       </c>
       <c r="F27" t="n">
+        <v>1.9276</v>
+      </c>
+      <c r="G27" t="n">
         <v>0.0408</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>0.1085</v>
       </c>
     </row>
@@ -1230,9 +1313,12 @@
         <v>0.9585</v>
       </c>
       <c r="F28" t="n">
+        <v>1.9317</v>
+      </c>
+      <c r="G28" t="n">
         <v>0.0569</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>0.1087</v>
       </c>
     </row>
@@ -1259,9 +1345,12 @@
         <v>0.9665</v>
       </c>
       <c r="F29" t="n">
+        <v>1.8744</v>
+      </c>
+      <c r="G29" t="n">
         <v>0.0529</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>0.1053</v>
       </c>
     </row>
@@ -1288,9 +1377,12 @@
         <v>0.9808</v>
       </c>
       <c r="F30" t="n">
+        <v>1.8823</v>
+      </c>
+      <c r="G30" t="n">
         <v>0.0428</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -1317,9 +1409,12 @@
         <v>0.9816</v>
       </c>
       <c r="F31" t="n">
+        <v>1.9146</v>
+      </c>
+      <c r="G31" t="n">
         <v>0.04</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>0.1077</v>
       </c>
     </row>
@@ -1346,9 +1441,12 @@
         <v>0.98</v>
       </c>
       <c r="F32" t="n">
+        <v>1.9075</v>
+      </c>
+      <c r="G32" t="n">
         <v>0.0396</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>0.1073</v>
       </c>
     </row>
@@ -1375,9 +1473,12 @@
         <v>0.9779</v>
       </c>
       <c r="F33" t="n">
+        <v>1.8915</v>
+      </c>
+      <c r="G33" t="n">
         <v>0.0432</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>0.1063</v>
       </c>
     </row>
@@ -1404,9 +1505,12 @@
         <v>0.9699</v>
       </c>
       <c r="F34" t="n">
+        <v>1.8324</v>
+      </c>
+      <c r="G34" t="n">
         <v>0.0471</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>0.1028</v>
       </c>
     </row>
@@ -1433,9 +1537,12 @@
         <v>0.9866</v>
       </c>
       <c r="F35" t="n">
+        <v>1.8019</v>
+      </c>
+      <c r="G35" t="n">
         <v>0.0368</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>0.1009</v>
       </c>
     </row>
@@ -1462,9 +1569,12 @@
         <v>0.9815</v>
       </c>
       <c r="F36" t="n">
+        <v>1.8065</v>
+      </c>
+      <c r="G36" t="n">
         <v>0.0416</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>0.1011</v>
       </c>
     </row>
@@ -1491,9 +1601,12 @@
         <v>0.9807</v>
       </c>
       <c r="F37" t="n">
+        <v>1.7548</v>
+      </c>
+      <c r="G37" t="n">
         <v>0.0352</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>0.0978</v>
       </c>
     </row>
@@ -1520,9 +1633,12 @@
         <v>0.9645</v>
       </c>
       <c r="F38" t="n">
+        <v>1.7314</v>
+      </c>
+      <c r="G38" t="n">
         <v>0.0443</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>0.0963</v>
       </c>
     </row>
@@ -1549,9 +1665,12 @@
         <v>0.9742</v>
       </c>
       <c r="F39" t="n">
+        <v>1.7549</v>
+      </c>
+      <c r="G39" t="n">
         <v>0.039</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>0.0978</v>
       </c>
     </row>
@@ -1578,9 +1697,12 @@
         <v>0.9758</v>
       </c>
       <c r="F40" t="n">
+        <v>1.7785</v>
+      </c>
+      <c r="G40" t="n">
         <v>0.0418</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>0.0994</v>
       </c>
     </row>
@@ -1607,9 +1729,12 @@
         <v>0.97</v>
       </c>
       <c r="F41" t="n">
+        <v>1.8314</v>
+      </c>
+      <c r="G41" t="n">
         <v>0.047</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>0.1027</v>
       </c>
     </row>
@@ -1636,9 +1761,12 @@
         <v>0.9813</v>
       </c>
       <c r="F42" t="n">
+        <v>1.7964</v>
+      </c>
+      <c r="G42" t="n">
         <v>0.0382</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>0.1005</v>
       </c>
     </row>
@@ -1665,9 +1793,12 @@
         <v>0.9821</v>
       </c>
       <c r="F43" t="n">
+        <v>1.8038</v>
+      </c>
+      <c r="G43" t="n">
         <v>0.0416</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>0.101</v>
       </c>
     </row>
@@ -1694,9 +1825,12 @@
         <v>0.9806</v>
       </c>
       <c r="F44" t="n">
+        <v>1.7393</v>
+      </c>
+      <c r="G44" t="n">
         <v>0.035</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>0.0968</v>
       </c>
     </row>
@@ -1723,9 +1857,12 @@
         <v>0.9641</v>
       </c>
       <c r="F45" t="n">
+        <v>1.7326</v>
+      </c>
+      <c r="G45" t="n">
         <v>0.0446</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>0.0964</v>
       </c>
     </row>
@@ -1752,9 +1889,12 @@
         <v>0.9776</v>
       </c>
       <c r="F46" t="n">
+        <v>1.7566</v>
+      </c>
+      <c r="G46" t="n">
         <v>0.0377</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>0.098</v>
       </c>
     </row>
@@ -1781,9 +1921,12 @@
         <v>0.9705</v>
       </c>
       <c r="F47" t="n">
+        <v>1.7692</v>
+      </c>
+      <c r="G47" t="n">
         <v>0.0425</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>0.0988</v>
       </c>
     </row>
@@ -1810,9 +1953,12 @@
         <v>0.9818</v>
       </c>
       <c r="F48" t="n">
+        <v>1.7957</v>
+      </c>
+      <c r="G48" t="n">
         <v>0.0405</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>0.1005</v>
       </c>
     </row>
@@ -1839,9 +1985,12 @@
         <v>0.9556</v>
       </c>
       <c r="F49" t="n">
+        <v>1.8048</v>
+      </c>
+      <c r="G49" t="n">
         <v>0.0524</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>0.101</v>
       </c>
     </row>
@@ -1868,9 +2017,12 @@
         <v>0.9792</v>
       </c>
       <c r="F50" t="n">
+        <v>1.9178</v>
+      </c>
+      <c r="G50" t="n">
         <v>0.0469</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>0.1079</v>
       </c>
     </row>
@@ -1897,9 +2049,12 @@
         <v>0.9105</v>
       </c>
       <c r="F51" t="n">
+        <v>2.0193</v>
+      </c>
+      <c r="G51" t="n">
         <v>0.0654</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>0.1137</v>
       </c>
     </row>
@@ -1926,9 +2081,12 @@
         <v>0.9262</v>
       </c>
       <c r="F52" t="n">
+        <v>2.0019</v>
+      </c>
+      <c r="G52" t="n">
         <v>0.0646</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>0.1127</v>
       </c>
     </row>
@@ -1955,9 +2113,12 @@
         <v>0.9599</v>
       </c>
       <c r="F53" t="n">
+        <v>1.9525</v>
+      </c>
+      <c r="G53" t="n">
         <v>0.057</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>0.1099</v>
       </c>
     </row>
@@ -1984,9 +2145,12 @@
         <v>0.949</v>
       </c>
       <c r="F54" t="n">
+        <v>1.9305</v>
+      </c>
+      <c r="G54" t="n">
         <v>0.0566</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>0.1086</v>
       </c>
     </row>
@@ -2013,9 +2177,12 @@
         <v>0.9752999999999999</v>
       </c>
       <c r="F55" t="n">
+        <v>1.8553</v>
+      </c>
+      <c r="G55" t="n">
         <v>0.0397</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>0.1042</v>
       </c>
     </row>
@@ -2042,9 +2209,12 @@
         <v>0.9804</v>
       </c>
       <c r="F56" t="n">
+        <v>1.8876</v>
+      </c>
+      <c r="G56" t="n">
         <v>0.0413</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>0.1061</v>
       </c>
     </row>
@@ -2071,9 +2241,12 @@
         <v>0.9822</v>
       </c>
       <c r="F57" t="n">
+        <v>1.924</v>
+      </c>
+      <c r="G57" t="n">
         <v>0.0387</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>0.1083</v>
       </c>
     </row>
@@ -2100,9 +2273,12 @@
         <v>0.8293</v>
       </c>
       <c r="F58" t="n">
+        <v>2.0013</v>
+      </c>
+      <c r="G58" t="n">
         <v>0.0722</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>0.1127</v>
       </c>
     </row>
@@ -2129,9 +2305,12 @@
         <v>0.8285</v>
       </c>
       <c r="F59" t="n">
+        <v>2.0015</v>
+      </c>
+      <c r="G59" t="n">
         <v>0.0722</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>0.1127</v>
       </c>
     </row>
@@ -2158,9 +2337,12 @@
         <v>0.8677</v>
       </c>
       <c r="F60" t="n">
+        <v>1.9972</v>
+      </c>
+      <c r="G60" t="n">
         <v>0.0659</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>0.1125</v>
       </c>
     </row>
@@ -2187,9 +2369,12 @@
         <v>0.9349</v>
       </c>
       <c r="F61" t="n">
+        <v>1.9995</v>
+      </c>
+      <c r="G61" t="n">
         <v>0.0521</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>0.1126</v>
       </c>
     </row>
@@ -2216,9 +2401,12 @@
         <v>0.9227</v>
       </c>
       <c r="F62" t="n">
+        <v>1.914</v>
+      </c>
+      <c r="G62" t="n">
         <v>0.0607</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>0.1077</v>
       </c>
     </row>
@@ -2245,9 +2433,12 @@
         <v>0.9637</v>
       </c>
       <c r="F63" t="n">
+        <v>1.8923</v>
+      </c>
+      <c r="G63" t="n">
         <v>0.0457</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>0.1064</v>
       </c>
     </row>
@@ -2274,9 +2465,12 @@
         <v>0.9177999999999999</v>
       </c>
       <c r="F64" t="n">
+        <v>1.9173</v>
+      </c>
+      <c r="G64" t="n">
         <v>0.0614</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>0.1079</v>
       </c>
     </row>
@@ -2303,9 +2497,12 @@
         <v>0.9553</v>
       </c>
       <c r="F65" t="n">
+        <v>1.9133</v>
+      </c>
+      <c r="G65" t="n">
         <v>0.0482</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>0.1076</v>
       </c>
     </row>
@@ -2332,9 +2529,12 @@
         <v>0.9774</v>
       </c>
       <c r="F66" t="n">
+        <v>1.9395</v>
+      </c>
+      <c r="G66" t="n">
         <v>0.0468</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>0.1092</v>
       </c>
     </row>
@@ -2361,9 +2561,12 @@
         <v>0.977</v>
       </c>
       <c r="F67" t="n">
+        <v>1.9053</v>
+      </c>
+      <c r="G67" t="n">
         <v>0.0445</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>0.1072</v>
       </c>
     </row>
@@ -2390,9 +2593,12 @@
         <v>0.9809</v>
       </c>
       <c r="F68" t="n">
+        <v>1.9094</v>
+      </c>
+      <c r="G68" t="n">
         <v>0.0395</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>0.1074</v>
       </c>
     </row>
@@ -2419,9 +2625,12 @@
         <v>0.9735</v>
       </c>
       <c r="F69" t="n">
+        <v>1.8703</v>
+      </c>
+      <c r="G69" t="n">
         <v>0.0424</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>0.1051</v>
       </c>
     </row>
@@ -2448,9 +2657,12 @@
         <v>0.9735</v>
       </c>
       <c r="F70" t="n">
+        <v>1.886</v>
+      </c>
+      <c r="G70" t="n">
         <v>0.0386</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>0.106</v>
       </c>
     </row>
@@ -2477,9 +2689,12 @@
         <v>0.9797</v>
       </c>
       <c r="F71" t="n">
+        <v>1.8542</v>
+      </c>
+      <c r="G71" t="n">
         <v>0.0416</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>0.1041</v>
       </c>
     </row>
@@ -2506,9 +2721,12 @@
         <v>0.9743000000000001</v>
       </c>
       <c r="F72" t="n">
+        <v>1.8906</v>
+      </c>
+      <c r="G72" t="n">
         <v>0.042</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>0.1063</v>
       </c>
     </row>
@@ -2535,9 +2753,12 @@
         <v>0.972</v>
       </c>
       <c r="F73" t="n">
+        <v>1.8561</v>
+      </c>
+      <c r="G73" t="n">
         <v>0.045</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>0.1042</v>
       </c>
     </row>
@@ -2564,9 +2785,12 @@
         <v>0.9658</v>
       </c>
       <c r="F74" t="n">
+        <v>1.8163</v>
+      </c>
+      <c r="G74" t="n">
         <v>0.0495</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>0.1018</v>
       </c>
     </row>
@@ -2593,9 +2817,12 @@
         <v>0.9004</v>
       </c>
       <c r="F75" t="n">
+        <v>1.9667</v>
+      </c>
+      <c r="G75" t="n">
         <v>0.0645</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>0.1107</v>
       </c>
     </row>
@@ -2622,9 +2849,12 @@
         <v>0.9004</v>
       </c>
       <c r="F76" t="n">
+        <v>1.9667</v>
+      </c>
+      <c r="G76" t="n">
         <v>0.0645</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>0.1107</v>
       </c>
     </row>
@@ -2651,9 +2881,12 @@
         <v>0.8231000000000001</v>
       </c>
       <c r="F77" t="n">
+        <v>2.0165</v>
+      </c>
+      <c r="G77" t="n">
         <v>0.0735</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>0.1135</v>
       </c>
     </row>
@@ -2680,9 +2913,12 @@
         <v>0.8224</v>
       </c>
       <c r="F78" t="n">
+        <v>2.0204</v>
+      </c>
+      <c r="G78" t="n">
         <v>0.0735</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>0.1138</v>
       </c>
     </row>
@@ -2709,9 +2945,12 @@
         <v>0.8196</v>
       </c>
       <c r="F79" t="n">
+        <v>2.0211</v>
+      </c>
+      <c r="G79" t="n">
         <v>0.0736</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>0.1138</v>
       </c>
     </row>
@@ -2738,9 +2977,12 @@
         <v>0.8226</v>
       </c>
       <c r="F80" t="n">
+        <v>2.0211</v>
+      </c>
+      <c r="G80" t="n">
         <v>0.07340000000000001</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>0.1138</v>
       </c>
     </row>
@@ -2767,9 +3009,12 @@
         <v>0.9741</v>
       </c>
       <c r="F81" t="n">
+        <v>1.9221</v>
+      </c>
+      <c r="G81" t="n">
         <v>0.0425</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>0.1081</v>
       </c>
     </row>
@@ -2796,9 +3041,12 @@
         <v>0.9712</v>
       </c>
       <c r="F82" t="n">
+        <v>1.919</v>
+      </c>
+      <c r="G82" t="n">
         <v>0.0426</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>0.108</v>
       </c>
     </row>
@@ -2825,9 +3073,12 @@
         <v>0.8912</v>
       </c>
       <c r="F83" t="n">
+        <v>1.9653</v>
+      </c>
+      <c r="G83" t="n">
         <v>0.06510000000000001</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>0.1106</v>
       </c>
     </row>
@@ -2854,9 +3105,12 @@
         <v>0.8923</v>
       </c>
       <c r="F84" t="n">
+        <v>1.9644</v>
+      </c>
+      <c r="G84" t="n">
         <v>0.0649</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>0.1106</v>
       </c>
     </row>
@@ -2883,9 +3137,12 @@
         <v>0.8537</v>
       </c>
       <c r="F85" t="n">
+        <v>1.9673</v>
+      </c>
+      <c r="G85" t="n">
         <v>0.0723</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>0.1108</v>
       </c>
     </row>
@@ -2912,9 +3169,12 @@
         <v>0.9324</v>
       </c>
       <c r="F86" t="n">
+        <v>1.9402</v>
+      </c>
+      <c r="G86" t="n">
         <v>0.06419999999999999</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>0.1092</v>
       </c>
     </row>
@@ -2941,9 +3201,12 @@
         <v>0.9791</v>
       </c>
       <c r="F87" t="n">
+        <v>1.9294</v>
+      </c>
+      <c r="G87" t="n">
         <v>0.0435</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>0.1086</v>
       </c>
     </row>
@@ -2963,16 +3226,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E88" t="n">
         <v>0.9609</v>
       </c>
       <c r="F88" t="n">
-        <v>0.053</v>
+        <v>1.8784</v>
       </c>
       <c r="G88" t="n">
+        <v>0.0531</v>
+      </c>
+      <c r="H88" t="n">
         <v>0.1056</v>
       </c>
     </row>
@@ -2999,9 +3265,12 @@
         <v>0.979</v>
       </c>
       <c r="F89" t="n">
+        <v>1.8866</v>
+      </c>
+      <c r="G89" t="n">
         <v>0.0425</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>0.106</v>
       </c>
     </row>
@@ -3028,9 +3297,12 @@
         <v>0.9823</v>
       </c>
       <c r="F90" t="n">
+        <v>1.8035</v>
+      </c>
+      <c r="G90" t="n">
         <v>0.0415</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>0.101</v>
       </c>
     </row>
@@ -3057,9 +3329,12 @@
         <v>0.9804</v>
       </c>
       <c r="F91" t="n">
+        <v>1.7416</v>
+      </c>
+      <c r="G91" t="n">
         <v>0.035</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>0.097</v>
       </c>
     </row>
@@ -3079,16 +3354,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E92" t="n">
         <v>0.9609</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0531</v>
+        <v>1.8784</v>
       </c>
       <c r="G92" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="H92" t="n">
         <v>0.1056</v>
       </c>
     </row>
@@ -3115,9 +3393,12 @@
         <v>0.9804</v>
       </c>
       <c r="F93" t="n">
+        <v>1.7416</v>
+      </c>
+      <c r="G93" t="n">
         <v>0.035</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>0.097</v>
       </c>
     </row>
@@ -3144,9 +3425,12 @@
         <v>0.9012</v>
       </c>
       <c r="F94" t="n">
+        <v>1.9911</v>
+      </c>
+      <c r="G94" t="n">
         <v>0.0614</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>0.1121</v>
       </c>
     </row>
@@ -3173,9 +3457,12 @@
         <v>0.8574000000000001</v>
       </c>
       <c r="F95" t="n">
+        <v>2.1271</v>
+      </c>
+      <c r="G95" t="n">
         <v>0.0721</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>0.1196</v>
       </c>
     </row>
@@ -3202,9 +3489,12 @@
         <v>0.8954</v>
       </c>
       <c r="F96" t="n">
+        <v>1.9942</v>
+      </c>
+      <c r="G96" t="n">
         <v>0.0626</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>0.1123</v>
       </c>
     </row>
@@ -3231,9 +3521,12 @@
         <v>0.8859</v>
       </c>
       <c r="F97" t="n">
+        <v>1.994</v>
+      </c>
+      <c r="G97" t="n">
         <v>0.0636</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>0.1123</v>
       </c>
     </row>
@@ -3260,9 +3553,12 @@
         <v>0.9824000000000001</v>
       </c>
       <c r="F98" t="n">
+        <v>1.9473</v>
+      </c>
+      <c r="G98" t="n">
         <v>0.0435</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>0.1096</v>
       </c>
     </row>
@@ -3289,9 +3585,12 @@
         <v>0.9782999999999999</v>
       </c>
       <c r="F99" t="n">
+        <v>1.942</v>
+      </c>
+      <c r="G99" t="n">
         <v>0.0436</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>0.1093</v>
       </c>
     </row>
@@ -3318,9 +3617,12 @@
         <v>0.9709</v>
       </c>
       <c r="F100" t="n">
+        <v>1.9352</v>
+      </c>
+      <c r="G100" t="n">
         <v>0.0468</v>
       </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>0.1089</v>
       </c>
     </row>
@@ -3347,9 +3649,12 @@
         <v>0.9755</v>
       </c>
       <c r="F101" t="n">
+        <v>1.9259</v>
+      </c>
+      <c r="G101" t="n">
         <v>0.0409</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>0.1084</v>
       </c>
     </row>
@@ -3376,9 +3681,12 @@
         <v>0.965</v>
       </c>
       <c r="F102" t="n">
+        <v>1.9492</v>
+      </c>
+      <c r="G102" t="n">
         <v>0.0474</v>
       </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>0.1097</v>
       </c>
     </row>
@@ -3405,9 +3713,12 @@
         <v>0.9823</v>
       </c>
       <c r="F103" t="n">
+        <v>1.9466</v>
+      </c>
+      <c r="G103" t="n">
         <v>0.0473</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>0.1096</v>
       </c>
     </row>
@@ -3434,9 +3745,12 @@
         <v>0.9835</v>
       </c>
       <c r="F104" t="n">
+        <v>1.919</v>
+      </c>
+      <c r="G104" t="n">
         <v>0.0399</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>0.108</v>
       </c>
     </row>
@@ -3463,9 +3777,12 @@
         <v>0.9818</v>
       </c>
       <c r="F105" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G105" t="n">
         <v>0.0436</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>0.1092</v>
       </c>
     </row>
@@ -3492,9 +3809,12 @@
         <v>0.9754</v>
       </c>
       <c r="F106" t="n">
+        <v>1.9435</v>
+      </c>
+      <c r="G106" t="n">
         <v>0.0466</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>0.1094</v>
       </c>
     </row>
@@ -3521,9 +3841,12 @@
         <v>0.9444</v>
       </c>
       <c r="F107" t="n">
+        <v>1.9375</v>
+      </c>
+      <c r="G107" t="n">
         <v>0.0564</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>0.109</v>
       </c>
     </row>
@@ -3550,9 +3873,12 @@
         <v>0.9893999999999999</v>
       </c>
       <c r="F108" t="n">
+        <v>1.8387</v>
+      </c>
+      <c r="G108" t="n">
         <v>0.0404</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>0.1031</v>
       </c>
     </row>
@@ -3579,9 +3905,12 @@
         <v>0.9858</v>
       </c>
       <c r="F109" t="n">
+        <v>1.8199</v>
+      </c>
+      <c r="G109" t="n">
         <v>0.0425</v>
       </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>0.102</v>
       </c>
     </row>
@@ -3608,9 +3937,12 @@
         <v>0.9781</v>
       </c>
       <c r="F110" t="n">
+        <v>1.7599</v>
+      </c>
+      <c r="G110" t="n">
         <v>0.04</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>0.0982</v>
       </c>
     </row>
@@ -3637,9 +3969,12 @@
         <v>0.9833</v>
       </c>
       <c r="F111" t="n">
+        <v>1.7303</v>
+      </c>
+      <c r="G111" t="n">
         <v>0.0361</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>0.09619999999999999</v>
       </c>
     </row>
@@ -3666,9 +4001,12 @@
         <v>0.9811</v>
       </c>
       <c r="F112" t="n">
+        <v>1.8353</v>
+      </c>
+      <c r="G112" t="n">
         <v>0.0447</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>0.1029</v>
       </c>
     </row>
@@ -3695,9 +4033,12 @@
         <v>0.9622000000000001</v>
       </c>
       <c r="F113" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="G113" t="n">
         <v>0.0544</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>0.1017</v>
       </c>
     </row>
@@ -3724,9 +4065,12 @@
         <v>0.9794</v>
       </c>
       <c r="F114" t="n">
+        <v>1.7476</v>
+      </c>
+      <c r="G114" t="n">
         <v>0.0393</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>0.0974</v>
       </c>
     </row>
@@ -3753,9 +4097,12 @@
         <v>0.9841</v>
       </c>
       <c r="F115" t="n">
+        <v>1.7305</v>
+      </c>
+      <c r="G115" t="n">
         <v>0.036</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>0.0963</v>
       </c>
     </row>
@@ -3782,9 +4129,12 @@
         <v>0.9762999999999999</v>
       </c>
       <c r="F116" t="n">
+        <v>1.9255</v>
+      </c>
+      <c r="G116" t="n">
         <v>0.0409</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>0.1083</v>
       </c>
     </row>
@@ -3811,9 +4161,12 @@
         <v>0.928</v>
       </c>
       <c r="F117" t="n">
+        <v>1.9446</v>
+      </c>
+      <c r="G117" t="n">
         <v>0.0577</v>
       </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>0.1095</v>
       </c>
     </row>
@@ -3840,9 +4193,12 @@
         <v>0.9818</v>
       </c>
       <c r="F118" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G118" t="n">
         <v>0.0436</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>0.1092</v>
       </c>
     </row>
@@ -3869,9 +4225,12 @@
         <v>0.9622000000000001</v>
       </c>
       <c r="F119" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="G119" t="n">
         <v>0.0544</v>
       </c>
-      <c r="G119" t="n">
+      <c r="H119" t="n">
         <v>0.1017</v>
       </c>
     </row>
@@ -3898,9 +4257,12 @@
         <v>0.9297</v>
       </c>
       <c r="F120" t="n">
+        <v>2.0037</v>
+      </c>
+      <c r="G120" t="n">
         <v>0.0617</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>0.1128</v>
       </c>
     </row>
@@ -3927,9 +4289,12 @@
         <v>0.9297</v>
       </c>
       <c r="F121" t="n">
+        <v>2.0037</v>
+      </c>
+      <c r="G121" t="n">
         <v>0.0617</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>0.1128</v>
       </c>
     </row>
@@ -3956,9 +4321,12 @@
         <v>0.9784</v>
       </c>
       <c r="F122" t="n">
+        <v>1.9604</v>
+      </c>
+      <c r="G122" t="n">
         <v>0.0424</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>0.1104</v>
       </c>
     </row>
@@ -3985,9 +4353,12 @@
         <v>0.9826</v>
       </c>
       <c r="F123" t="n">
+        <v>1.8139</v>
+      </c>
+      <c r="G123" t="n">
         <v>0.0382</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>0.1016</v>
       </c>
     </row>
@@ -4014,9 +4385,12 @@
         <v>0.9777</v>
       </c>
       <c r="F124" t="n">
+        <v>1.7733</v>
+      </c>
+      <c r="G124" t="n">
         <v>0.0398</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>0.099</v>
       </c>
     </row>
@@ -4043,9 +4417,12 @@
         <v>0.9021</v>
       </c>
       <c r="F125" t="n">
+        <v>1.9873</v>
+      </c>
+      <c r="G125" t="n">
         <v>0.0612</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>0.1119</v>
       </c>
     </row>
@@ -4072,9 +4449,12 @@
         <v>0.9686</v>
       </c>
       <c r="F126" t="n">
+        <v>1.9389</v>
+      </c>
+      <c r="G126" t="n">
         <v>0.047</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>0.1091</v>
       </c>
     </row>
@@ -4101,9 +4481,12 @@
         <v>0.8939</v>
       </c>
       <c r="F127" t="n">
+        <v>2.0079</v>
+      </c>
+      <c r="G127" t="n">
         <v>0.06270000000000001</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>0.1131</v>
       </c>
     </row>
@@ -4130,9 +4513,12 @@
         <v>0.959</v>
       </c>
       <c r="F128" t="n">
+        <v>1.9112</v>
+      </c>
+      <c r="G128" t="n">
         <v>0.0469</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>0.1075</v>
       </c>
     </row>
@@ -4159,9 +4545,12 @@
         <v>0.9681999999999999</v>
       </c>
       <c r="F129" t="n">
+        <v>1.9216</v>
+      </c>
+      <c r="G129" t="n">
         <v>0.0442</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>0.1081</v>
       </c>
     </row>
@@ -4188,9 +4577,12 @@
         <v>0.9665</v>
       </c>
       <c r="F130" t="n">
+        <v>1.9283</v>
+      </c>
+      <c r="G130" t="n">
         <v>0.0471</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>0.1085</v>
       </c>
     </row>
@@ -4217,9 +4609,12 @@
         <v>0.9668</v>
       </c>
       <c r="F131" t="n">
+        <v>1.9289</v>
+      </c>
+      <c r="G131" t="n">
         <v>0.0467</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>0.1085</v>
       </c>
     </row>
@@ -4246,9 +4641,12 @@
         <v>0.9585</v>
       </c>
       <c r="F132" t="n">
+        <v>1.9202</v>
+      </c>
+      <c r="G132" t="n">
         <v>0.0478</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>0.108</v>
       </c>
     </row>
@@ -4275,9 +4673,12 @@
         <v>0.9713000000000001</v>
       </c>
       <c r="F133" t="n">
+        <v>1.9213</v>
+      </c>
+      <c r="G133" t="n">
         <v>0.0447</v>
       </c>
-      <c r="G133" t="n">
+      <c r="H133" t="n">
         <v>0.1081</v>
       </c>
     </row>
@@ -4304,9 +4705,12 @@
         <v>0.966</v>
       </c>
       <c r="F134" t="n">
+        <v>1.9224</v>
+      </c>
+      <c r="G134" t="n">
         <v>0.0469</v>
       </c>
-      <c r="G134" t="n">
+      <c r="H134" t="n">
         <v>0.1082</v>
       </c>
     </row>
@@ -4333,9 +4737,12 @@
         <v>0.9552</v>
       </c>
       <c r="F135" t="n">
+        <v>1.9196</v>
+      </c>
+      <c r="G135" t="n">
         <v>0.05</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>0.108</v>
       </c>
     </row>
@@ -4362,9 +4769,12 @@
         <v>0.9666</v>
       </c>
       <c r="F136" t="n">
+        <v>1.932</v>
+      </c>
+      <c r="G136" t="n">
         <v>0.0464</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>0.1087</v>
       </c>
     </row>
@@ -4391,9 +4801,12 @@
         <v>0.9821</v>
       </c>
       <c r="F137" t="n">
+        <v>1.9324</v>
+      </c>
+      <c r="G137" t="n">
         <v>0.0436</v>
       </c>
-      <c r="G137" t="n">
+      <c r="H137" t="n">
         <v>0.1087</v>
       </c>
     </row>
@@ -4420,9 +4833,12 @@
         <v>0.9621</v>
       </c>
       <c r="F138" t="n">
+        <v>1.9369</v>
+      </c>
+      <c r="G138" t="n">
         <v>0.0539</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>0.109</v>
       </c>
     </row>
@@ -4449,9 +4865,12 @@
         <v>0.9833</v>
       </c>
       <c r="F139" t="n">
+        <v>1.9671</v>
+      </c>
+      <c r="G139" t="n">
         <v>0.0442</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>0.1108</v>
       </c>
     </row>
@@ -4478,9 +4897,12 @@
         <v>0.9879</v>
       </c>
       <c r="F140" t="n">
+        <v>1.8424</v>
+      </c>
+      <c r="G140" t="n">
         <v>0.0386</v>
       </c>
-      <c r="G140" t="n">
+      <c r="H140" t="n">
         <v>0.1034</v>
       </c>
     </row>
@@ -4507,9 +4929,12 @@
         <v>0.9869</v>
       </c>
       <c r="F141" t="n">
+        <v>1.8058</v>
+      </c>
+      <c r="G141" t="n">
         <v>0.0359</v>
       </c>
-      <c r="G141" t="n">
+      <c r="H141" t="n">
         <v>0.1011</v>
       </c>
     </row>
@@ -4536,9 +4961,12 @@
         <v>0.9621</v>
       </c>
       <c r="F142" t="n">
+        <v>1.9369</v>
+      </c>
+      <c r="G142" t="n">
         <v>0.0539</v>
       </c>
-      <c r="G142" t="n">
+      <c r="H142" t="n">
         <v>0.109</v>
       </c>
     </row>
@@ -4565,9 +4993,12 @@
         <v>0.9648</v>
       </c>
       <c r="F143" t="n">
+        <v>2.0105</v>
+      </c>
+      <c r="G143" t="n">
         <v>0.0573</v>
       </c>
-      <c r="G143" t="n">
+      <c r="H143" t="n">
         <v>0.1132</v>
       </c>
     </row>
@@ -4594,9 +5025,12 @@
         <v>0.9606</v>
       </c>
       <c r="F144" t="n">
+        <v>1.9918</v>
+      </c>
+      <c r="G144" t="n">
         <v>0.0579</v>
       </c>
-      <c r="G144" t="n">
+      <c r="H144" t="n">
         <v>0.1122</v>
       </c>
     </row>
@@ -4623,9 +5057,12 @@
         <v>0.9869</v>
       </c>
       <c r="F145" t="n">
+        <v>1.8058</v>
+      </c>
+      <c r="G145" t="n">
         <v>0.0359</v>
       </c>
-      <c r="G145" t="n">
+      <c r="H145" t="n">
         <v>0.1011</v>
       </c>
     </row>
@@ -4652,9 +5089,12 @@
         <v>0.8943</v>
       </c>
       <c r="F146" t="n">
+        <v>2.0182</v>
+      </c>
+      <c r="G146" t="n">
         <v>0.0624</v>
       </c>
-      <c r="G146" t="n">
+      <c r="H146" t="n">
         <v>0.1136</v>
       </c>
     </row>
@@ -4681,9 +5121,12 @@
         <v>0.8932</v>
       </c>
       <c r="F147" t="n">
+        <v>2.0149</v>
+      </c>
+      <c r="G147" t="n">
         <v>0.0626</v>
       </c>
-      <c r="G147" t="n">
+      <c r="H147" t="n">
         <v>0.1135</v>
       </c>
     </row>
@@ -4710,9 +5153,12 @@
         <v>0.8884</v>
       </c>
       <c r="F148" t="n">
+        <v>2.0165</v>
+      </c>
+      <c r="G148" t="n">
         <v>0.0629</v>
       </c>
-      <c r="G148" t="n">
+      <c r="H148" t="n">
         <v>0.1136</v>
       </c>
     </row>
@@ -4739,9 +5185,12 @@
         <v>0.8892</v>
       </c>
       <c r="F149" t="n">
+        <v>2.0215</v>
+      </c>
+      <c r="G149" t="n">
         <v>0.063</v>
       </c>
-      <c r="G149" t="n">
+      <c r="H149" t="n">
         <v>0.1138</v>
       </c>
     </row>
@@ -4768,9 +5217,12 @@
         <v>0.8917</v>
       </c>
       <c r="F150" t="n">
+        <v>2.0088</v>
+      </c>
+      <c r="G150" t="n">
         <v>0.06320000000000001</v>
       </c>
-      <c r="G150" t="n">
+      <c r="H150" t="n">
         <v>0.1131</v>
       </c>
     </row>
@@ -4797,9 +5249,12 @@
         <v>0.8923</v>
       </c>
       <c r="F151" t="n">
+        <v>2.017</v>
+      </c>
+      <c r="G151" t="n">
         <v>0.063</v>
       </c>
-      <c r="G151" t="n">
+      <c r="H151" t="n">
         <v>0.1136</v>
       </c>
     </row>
@@ -4826,9 +5281,12 @@
         <v>0.8929</v>
       </c>
       <c r="F152" t="n">
+        <v>2.0204</v>
+      </c>
+      <c r="G152" t="n">
         <v>0.06279999999999999</v>
       </c>
-      <c r="G152" t="n">
+      <c r="H152" t="n">
         <v>0.1138</v>
       </c>
     </row>
@@ -4855,9 +5313,12 @@
         <v>0.8778</v>
       </c>
       <c r="F153" t="n">
+        <v>2.0237</v>
+      </c>
+      <c r="G153" t="n">
         <v>0.0665</v>
       </c>
-      <c r="G153" t="n">
+      <c r="H153" t="n">
         <v>0.114</v>
       </c>
     </row>
@@ -4884,9 +5345,12 @@
         <v>0.8919</v>
       </c>
       <c r="F154" t="n">
+        <v>2.0238</v>
+      </c>
+      <c r="G154" t="n">
         <v>0.0629</v>
       </c>
-      <c r="G154" t="n">
+      <c r="H154" t="n">
         <v>0.114</v>
       </c>
     </row>
@@ -4913,9 +5377,12 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="F155" t="n">
+        <v>1.9373</v>
+      </c>
+      <c r="G155" t="n">
         <v>0.0569</v>
       </c>
-      <c r="G155" t="n">
+      <c r="H155" t="n">
         <v>0.109</v>
       </c>
     </row>
@@ -4942,9 +5409,12 @@
         <v>0.9584</v>
       </c>
       <c r="F156" t="n">
+        <v>1.9664</v>
+      </c>
+      <c r="G156" t="n">
         <v>0.0471</v>
       </c>
-      <c r="G156" t="n">
+      <c r="H156" t="n">
         <v>0.1107</v>
       </c>
     </row>
@@ -4971,9 +5441,12 @@
         <v>0.9204</v>
       </c>
       <c r="F157" t="n">
+        <v>1.9756</v>
+      </c>
+      <c r="G157" t="n">
         <v>0.0595</v>
       </c>
-      <c r="G157" t="n">
+      <c r="H157" t="n">
         <v>0.1112</v>
       </c>
     </row>
@@ -5000,9 +5473,12 @@
         <v>0.9565</v>
       </c>
       <c r="F158" t="n">
+        <v>1.9997</v>
+      </c>
+      <c r="G158" t="n">
         <v>0.0537</v>
       </c>
-      <c r="G158" t="n">
+      <c r="H158" t="n">
         <v>0.1126</v>
       </c>
     </row>
@@ -5029,9 +5505,12 @@
         <v>0.9115</v>
       </c>
       <c r="F159" t="n">
+        <v>1.9695</v>
+      </c>
+      <c r="G159" t="n">
         <v>0.063</v>
       </c>
-      <c r="G159" t="n">
+      <c r="H159" t="n">
         <v>0.1109</v>
       </c>
     </row>
@@ -5058,9 +5537,12 @@
         <v>0.8216</v>
       </c>
       <c r="F160" t="n">
+        <v>2.0554</v>
+      </c>
+      <c r="G160" t="n">
         <v>0.0751</v>
       </c>
-      <c r="G160" t="n">
+      <c r="H160" t="n">
         <v>0.1157</v>
       </c>
     </row>
@@ -5087,9 +5569,12 @@
         <v>0.8659</v>
       </c>
       <c r="F161" t="n">
+        <v>2.0486</v>
+      </c>
+      <c r="G161" t="n">
         <v>0.0687</v>
       </c>
-      <c r="G161" t="n">
+      <c r="H161" t="n">
         <v>0.1153</v>
       </c>
     </row>
@@ -5116,9 +5601,12 @@
         <v>0.9655</v>
       </c>
       <c r="F162" t="n">
+        <v>1.9808</v>
+      </c>
+      <c r="G162" t="n">
         <v>0.0491</v>
       </c>
-      <c r="G162" t="n">
+      <c r="H162" t="n">
         <v>0.1115</v>
       </c>
     </row>
@@ -5145,9 +5633,12 @@
         <v>0.9818</v>
       </c>
       <c r="F163" t="n">
+        <v>1.9181</v>
+      </c>
+      <c r="G163" t="n">
         <v>0.0431</v>
       </c>
-      <c r="G163" t="n">
+      <c r="H163" t="n">
         <v>0.1079</v>
       </c>
     </row>
@@ -5174,9 +5665,12 @@
         <v>0.9881</v>
       </c>
       <c r="F164" t="n">
+        <v>1.8428</v>
+      </c>
+      <c r="G164" t="n">
         <v>0.0386</v>
       </c>
-      <c r="G164" t="n">
+      <c r="H164" t="n">
         <v>0.1034</v>
       </c>
     </row>
@@ -5203,9 +5697,12 @@
         <v>0.9021</v>
       </c>
       <c r="F165" t="n">
+        <v>1.9873</v>
+      </c>
+      <c r="G165" t="n">
         <v>0.0612</v>
       </c>
-      <c r="G165" t="n">
+      <c r="H165" t="n">
         <v>0.1119</v>
       </c>
     </row>
@@ -5232,9 +5729,12 @@
         <v>0.8536</v>
       </c>
       <c r="F166" t="n">
+        <v>2.1281</v>
+      </c>
+      <c r="G166" t="n">
         <v>0.0727</v>
       </c>
-      <c r="G166" t="n">
+      <c r="H166" t="n">
         <v>0.1196</v>
       </c>
     </row>
@@ -5261,9 +5761,12 @@
         <v>0.9641</v>
       </c>
       <c r="F167" t="n">
+        <v>1.8484</v>
+      </c>
+      <c r="G167" t="n">
         <v>0.0512</v>
       </c>
-      <c r="G167" t="n">
+      <c r="H167" t="n">
         <v>0.1037</v>
       </c>
     </row>
@@ -5290,9 +5793,12 @@
         <v>0.9846</v>
       </c>
       <c r="F168" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="G168" t="n">
         <v>0.0385</v>
       </c>
-      <c r="G168" t="n">
+      <c r="H168" t="n">
         <v>0.1027</v>
       </c>
     </row>
@@ -5319,9 +5825,12 @@
         <v>0.98</v>
       </c>
       <c r="F169" t="n">
+        <v>1.8122</v>
+      </c>
+      <c r="G169" t="n">
         <v>0.0394</v>
       </c>
-      <c r="G169" t="n">
+      <c r="H169" t="n">
         <v>0.1015</v>
       </c>
     </row>
@@ -5348,9 +5857,12 @@
         <v>0.982</v>
       </c>
       <c r="F170" t="n">
+        <v>1.8188</v>
+      </c>
+      <c r="G170" t="n">
         <v>0.0382</v>
       </c>
-      <c r="G170" t="n">
+      <c r="H170" t="n">
         <v>0.1019</v>
       </c>
     </row>
@@ -5377,9 +5889,12 @@
         <v>0.9815</v>
       </c>
       <c r="F171" t="n">
+        <v>1.7716</v>
+      </c>
+      <c r="G171" t="n">
         <v>0.0382</v>
       </c>
-      <c r="G171" t="n">
+      <c r="H171" t="n">
         <v>0.0989</v>
       </c>
     </row>
@@ -5406,9 +5921,12 @@
         <v>0.9338</v>
       </c>
       <c r="F172" t="n">
+        <v>2.0017</v>
+      </c>
+      <c r="G172" t="n">
         <v>0.062</v>
       </c>
-      <c r="G172" t="n">
+      <c r="H172" t="n">
         <v>0.1127</v>
       </c>
     </row>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/ratio.alpha.natif/RANDOMSEARCH_DETAILS_ratio.alpha.natif.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/ratio.alpha.natif/RANDOMSEARCH_DETAILS_ratio.alpha.natif.xlsx
@@ -474,20 +474,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9676</v>
+        <v>0.9709</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8183</v>
+        <v>0.1445</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0479</v>
+        <v>0.0444</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1019</v>
+        <v>0.1073</v>
       </c>
     </row>
     <row r="3">
@@ -506,20 +506,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.9796</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7881</v>
+        <v>0.1725</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0387</v>
+        <v>0.0431</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1</v>
+        <v>0.1055</v>
       </c>
     </row>
     <row r="4">
@@ -538,20 +538,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9012</v>
+        <v>0.9036</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9911</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0614</v>
+        <v>0.0616</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1121</v>
+        <v>0.1155</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +570,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8262</v>
+        <v>0.8991</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9908</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0596</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1121</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="6">
@@ -602,20 +602,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8286</v>
+        <v>0.8858</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9986</v>
+        <v>0.1057</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0721</v>
+        <v>0.0617</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1125</v>
+        <v>0.1097</v>
       </c>
     </row>
     <row r="7">
@@ -634,20 +634,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8538</v>
+        <v>0.9133</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0911</v>
+        <v>-0.111</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0746</v>
+        <v>0.0643</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1176</v>
+        <v>0.1223</v>
       </c>
     </row>
     <row r="8">
@@ -666,20 +666,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9702</v>
+        <v>0.9735</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8937</v>
+        <v>0.0504</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0442</v>
+        <v>0.041</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1065</v>
+        <v>0.1131</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9775</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>1.799</v>
+        <v>0.1547</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0427</v>
+        <v>0.0406</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1007</v>
+        <v>0.1067</v>
       </c>
     </row>
     <row r="10">
@@ -730,20 +730,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9223</v>
+        <v>0.9716</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8883</v>
+        <v>0.0963</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0584</v>
+        <v>0.0407</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1061</v>
+        <v>0.1103</v>
       </c>
     </row>
     <row r="11">
@@ -762,20 +762,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9151</v>
+        <v>0.9096</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8624</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0589</v>
+        <v>0.0602</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1046</v>
+        <v>0.1114</v>
       </c>
     </row>
     <row r="12">
@@ -794,20 +794,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.9142</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8834</v>
+        <v>0.0555</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0591</v>
+        <v>0.0598</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1059</v>
+        <v>0.1127</v>
       </c>
     </row>
     <row r="13">
@@ -826,20 +826,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9615</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8805</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0442</v>
+        <v>0.0455</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1057</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="14">
@@ -858,20 +858,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.9147</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8803</v>
+        <v>0.0738</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0595</v>
+        <v>0.0593</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1057</v>
+        <v>0.1116</v>
       </c>
     </row>
     <row r="15">
@@ -890,20 +890,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9144</v>
+        <v>0.9154</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8781</v>
+        <v>0.0639</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0594</v>
+        <v>0.0592</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1055</v>
+        <v>0.1122</v>
       </c>
     </row>
     <row r="16">
@@ -922,20 +922,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9149</v>
+        <v>0.9116</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8636</v>
+        <v>0.0698</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0589</v>
+        <v>0.0606</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1047</v>
+        <v>0.1119</v>
       </c>
     </row>
     <row r="17">
@@ -954,20 +954,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9137</v>
+        <v>0.9244</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8753</v>
+        <v>0.0761</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0589</v>
+        <v>0.058</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1054</v>
+        <v>0.1115</v>
       </c>
     </row>
     <row r="18">
@@ -986,20 +986,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9801</v>
+        <v>0.9856</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9231</v>
+        <v>0.0068</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0407</v>
+        <v>0.0406</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1082</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9611</v>
+        <v>0.9712</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8943</v>
+        <v>0.046</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0541</v>
+        <v>0.0489</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1065</v>
+        <v>0.1133</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9815</v>
+        <v>0.9789</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8895</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0424</v>
+        <v>0.0442</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1062</v>
+        <v>0.1109</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9549</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9098</v>
+        <v>0.0302</v>
       </c>
       <c r="G21" t="n">
-        <v>0.055</v>
+        <v>0.041</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1074</v>
+        <v>0.1142</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9351</v>
+        <v>0.9658</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9208</v>
+        <v>0.0298</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0577</v>
+        <v>0.0488</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1081</v>
+        <v>0.1143</v>
       </c>
     </row>
     <row r="23">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9728</v>
+        <v>0.9775</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9228</v>
+        <v>0.0318</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0446</v>
+        <v>0.0414</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1082</v>
+        <v>0.1142</v>
       </c>
     </row>
     <row r="24">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9384</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>1.924</v>
+        <v>0.0316</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0585</v>
+        <v>0.0487</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1083</v>
+        <v>0.1142</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9649</v>
+        <v>0.9786</v>
       </c>
       <c r="F25" t="n">
-        <v>1.9376</v>
+        <v>0.0452</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0478</v>
+        <v>0.0408</v>
       </c>
       <c r="H25" t="n">
-        <v>0.109</v>
+        <v>0.1134</v>
       </c>
     </row>
     <row r="26">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9811</v>
+        <v>0.9354</v>
       </c>
       <c r="F26" t="n">
-        <v>1.9245</v>
+        <v>-0.0047</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0415</v>
+        <v>0.0658</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1083</v>
+        <v>0.1163</v>
       </c>
     </row>
     <row r="27">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9831</v>
+        <v>0.9768</v>
       </c>
       <c r="F27" t="n">
-        <v>1.9276</v>
+        <v>0.016</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0408</v>
+        <v>0.0485</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1085</v>
+        <v>0.1151</v>
       </c>
     </row>
     <row r="28">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9585</v>
+        <v>0.974</v>
       </c>
       <c r="F28" t="n">
-        <v>1.9317</v>
+        <v>0.0075</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0569</v>
+        <v>0.049</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1087</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="29">
@@ -1338,20 +1338,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9665</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>1.8744</v>
+        <v>0.0844</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0529</v>
+        <v>0.0435</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1053</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9808</v>
+        <v>0.9589</v>
       </c>
       <c r="F30" t="n">
-        <v>1.8823</v>
+        <v>0.0453</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0428</v>
+        <v>0.0554</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1058</v>
+        <v>0.1134</v>
       </c>
     </row>
     <row r="31">
@@ -1402,20 +1402,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9816</v>
+        <v>0.9688</v>
       </c>
       <c r="F31" t="n">
-        <v>1.9146</v>
+        <v>0.0286</v>
       </c>
       <c r="G31" t="n">
-        <v>0.04</v>
+        <v>0.0483</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1077</v>
+        <v>0.1143</v>
       </c>
     </row>
     <row r="32">
@@ -1434,20 +1434,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.98</v>
+        <v>0.9679</v>
       </c>
       <c r="F32" t="n">
-        <v>1.9075</v>
+        <v>0.0467</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0396</v>
+        <v>0.0486</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1073</v>
+        <v>0.1133</v>
       </c>
     </row>
     <row r="33">
@@ -1470,16 +1470,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9779</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>1.8915</v>
+        <v>0.0397</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0432</v>
+        <v>0.0441</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1063</v>
+        <v>0.1137</v>
       </c>
     </row>
     <row r="34">
@@ -1498,20 +1498,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9699</v>
+        <v>0.9859</v>
       </c>
       <c r="F34" t="n">
-        <v>1.8324</v>
+        <v>0.1342</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0471</v>
+        <v>0.0394</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1028</v>
+        <v>0.1079</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9866</v>
+        <v>0.9852</v>
       </c>
       <c r="F35" t="n">
-        <v>1.8019</v>
+        <v>0.1564</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0368</v>
+        <v>0.0397</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1009</v>
+        <v>0.1066</v>
       </c>
     </row>
     <row r="36">
@@ -1562,20 +1562,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9815</v>
+        <v>0.985</v>
       </c>
       <c r="F36" t="n">
-        <v>1.8065</v>
+        <v>0.1705</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0416</v>
+        <v>0.04</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1011</v>
+        <v>0.1057</v>
       </c>
     </row>
     <row r="37">
@@ -1594,20 +1594,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9807</v>
+        <v>0.9795</v>
       </c>
       <c r="F37" t="n">
-        <v>1.7548</v>
+        <v>0.1874</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0352</v>
+        <v>0.0394</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0978</v>
+        <v>0.1046</v>
       </c>
     </row>
     <row r="38">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9645</v>
+        <v>0.9782</v>
       </c>
       <c r="F38" t="n">
-        <v>1.7314</v>
+        <v>0.189</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0443</v>
+        <v>0.0434</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0963</v>
+        <v>0.1045</v>
       </c>
     </row>
     <row r="39">
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9742</v>
+        <v>0.9759</v>
       </c>
       <c r="F39" t="n">
-        <v>1.7549</v>
+        <v>0.1788</v>
       </c>
       <c r="G39" t="n">
-        <v>0.039</v>
+        <v>0.0416</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0978</v>
+        <v>0.1051</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9758</v>
+        <v>0.984</v>
       </c>
       <c r="F40" t="n">
-        <v>1.7785</v>
+        <v>0.1366</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0418</v>
+        <v>0.0371</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0994</v>
+        <v>0.1078</v>
       </c>
     </row>
     <row r="41">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.97</v>
+        <v>0.9862</v>
       </c>
       <c r="F41" t="n">
-        <v>1.8314</v>
+        <v>0.1367</v>
       </c>
       <c r="G41" t="n">
-        <v>0.047</v>
+        <v>0.0394</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1027</v>
+        <v>0.1078</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9813</v>
+        <v>0.9852</v>
       </c>
       <c r="F42" t="n">
-        <v>1.7964</v>
+        <v>0.1573</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0382</v>
+        <v>0.04</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1005</v>
+        <v>0.1065</v>
       </c>
     </row>
     <row r="43">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9821</v>
+        <v>0.9826</v>
       </c>
       <c r="F43" t="n">
-        <v>1.8038</v>
+        <v>0.1721</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0416</v>
+        <v>0.04</v>
       </c>
       <c r="H43" t="n">
-        <v>0.101</v>
+        <v>0.1056</v>
       </c>
     </row>
     <row r="44">
@@ -1818,20 +1818,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9806</v>
+        <v>0.9792</v>
       </c>
       <c r="F44" t="n">
-        <v>1.7393</v>
+        <v>0.1852</v>
       </c>
       <c r="G44" t="n">
-        <v>0.035</v>
+        <v>0.0393</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0968</v>
+        <v>0.1047</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9641</v>
+        <v>0.9856</v>
       </c>
       <c r="F45" t="n">
-        <v>1.7326</v>
+        <v>0.1754</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0446</v>
+        <v>0.036</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0964</v>
+        <v>0.1053</v>
       </c>
     </row>
     <row r="46">
@@ -1882,20 +1882,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9776</v>
+        <v>0.9768</v>
       </c>
       <c r="F46" t="n">
-        <v>1.7566</v>
+        <v>0.1838</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0377</v>
+        <v>0.0418</v>
       </c>
       <c r="H46" t="n">
-        <v>0.098</v>
+        <v>0.1048</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9705</v>
+        <v>0.9707</v>
       </c>
       <c r="F47" t="n">
-        <v>1.7692</v>
+        <v>0.1454</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0425</v>
+        <v>0.0439</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0988</v>
+        <v>0.1073</v>
       </c>
     </row>
     <row r="48">
@@ -1946,20 +1946,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9818</v>
+        <v>0.9897</v>
       </c>
       <c r="F48" t="n">
-        <v>1.7957</v>
+        <v>0.1913</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0405</v>
+        <v>0.0365</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1005</v>
+        <v>0.1043</v>
       </c>
     </row>
     <row r="49">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9556</v>
+        <v>0.9875</v>
       </c>
       <c r="F49" t="n">
-        <v>1.8048</v>
+        <v>0.1678</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0524</v>
+        <v>0.0371</v>
       </c>
       <c r="H49" t="n">
-        <v>0.101</v>
+        <v>0.1058</v>
       </c>
     </row>
     <row r="50">
@@ -2010,20 +2010,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9792</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>1.9178</v>
+        <v>0.0458</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0469</v>
+        <v>0.0417</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1079</v>
+        <v>0.1133</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.9105</v>
+        <v>0.8813</v>
       </c>
       <c r="F51" t="n">
-        <v>2.0193</v>
+        <v>-0.0473</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0654</v>
+        <v>0.0741</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1137</v>
+        <v>0.1187</v>
       </c>
     </row>
     <row r="52">
@@ -2074,20 +2074,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.9262</v>
+        <v>0.8773</v>
       </c>
       <c r="F52" t="n">
-        <v>2.0019</v>
+        <v>-0.0408</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0646</v>
+        <v>0.0737</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1127</v>
+        <v>0.1184</v>
       </c>
     </row>
     <row r="53">
@@ -2110,16 +2110,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9599</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>1.9525</v>
+        <v>-0.0475</v>
       </c>
       <c r="G53" t="n">
-        <v>0.057</v>
+        <v>0.0583</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1099</v>
+        <v>0.1187</v>
       </c>
     </row>
     <row r="54">
@@ -2138,20 +2138,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.949</v>
+        <v>0.9421</v>
       </c>
       <c r="F54" t="n">
-        <v>1.9305</v>
+        <v>-0.0063</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0566</v>
+        <v>0.0577</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1086</v>
+        <v>0.1164</v>
       </c>
     </row>
     <row r="55">
@@ -2170,20 +2170,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9755</v>
       </c>
       <c r="F55" t="n">
-        <v>1.8553</v>
+        <v>0.1245</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0397</v>
+        <v>0.0404</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1042</v>
+        <v>0.1086</v>
       </c>
     </row>
     <row r="56">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9804</v>
+        <v>0.9571</v>
       </c>
       <c r="F56" t="n">
-        <v>1.8876</v>
+        <v>0.081</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0413</v>
+        <v>0.057</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1061</v>
+        <v>0.1112</v>
       </c>
     </row>
     <row r="57">
@@ -2234,20 +2234,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9822</v>
+        <v>0.9473</v>
       </c>
       <c r="F57" t="n">
-        <v>1.924</v>
+        <v>0.0591</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0387</v>
+        <v>0.0565</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1083</v>
+        <v>0.1125</v>
       </c>
     </row>
     <row r="58">
@@ -2266,20 +2266,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8293</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>2.0013</v>
+        <v>0.105</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0722</v>
+        <v>0.0619</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1127</v>
+        <v>0.1098</v>
       </c>
     </row>
     <row r="59">
@@ -2298,20 +2298,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8285</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>2.0015</v>
+        <v>0.1049</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0722</v>
+        <v>0.062</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1127</v>
+        <v>0.1098</v>
       </c>
     </row>
     <row r="60">
@@ -2330,20 +2330,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.8677</v>
+        <v>0.8847</v>
       </c>
       <c r="F60" t="n">
-        <v>1.9972</v>
+        <v>0.1014</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0659</v>
+        <v>0.0619</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1125</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="61">
@@ -2362,20 +2362,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.9349</v>
+        <v>0.8857</v>
       </c>
       <c r="F61" t="n">
-        <v>1.9995</v>
+        <v>0.1045</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0521</v>
+        <v>0.0617</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1126</v>
+        <v>0.1098</v>
       </c>
     </row>
     <row r="62">
@@ -2394,20 +2394,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.9227</v>
+        <v>0.9681</v>
       </c>
       <c r="F62" t="n">
-        <v>1.914</v>
+        <v>0.0735</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0607</v>
+        <v>0.045</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1077</v>
+        <v>0.1117</v>
       </c>
     </row>
     <row r="63">
@@ -2426,20 +2426,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.9637</v>
+        <v>0.9687</v>
       </c>
       <c r="F63" t="n">
-        <v>1.8923</v>
+        <v>0.0849</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0457</v>
+        <v>0.0439</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1064</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="64">
@@ -2458,20 +2458,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9314</v>
       </c>
       <c r="F64" t="n">
-        <v>1.9173</v>
+        <v>0.1022</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0614</v>
+        <v>0.0556</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1079</v>
+        <v>0.1099</v>
       </c>
     </row>
     <row r="65">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.9553</v>
+        <v>0.9681</v>
       </c>
       <c r="F65" t="n">
-        <v>1.9133</v>
+        <v>0.1001</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0482</v>
+        <v>0.0418</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1076</v>
+        <v>0.1101</v>
       </c>
     </row>
     <row r="66">
@@ -2526,16 +2526,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9774</v>
+        <v>0.9752</v>
       </c>
       <c r="F66" t="n">
-        <v>1.9395</v>
+        <v>0.0381</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0468</v>
+        <v>0.0475</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1092</v>
+        <v>0.1138</v>
       </c>
     </row>
     <row r="67">
@@ -2554,20 +2554,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.977</v>
+        <v>0.9768</v>
       </c>
       <c r="F67" t="n">
-        <v>1.9053</v>
+        <v>0.0738</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0445</v>
+        <v>0.0429</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1072</v>
+        <v>0.1116</v>
       </c>
     </row>
     <row r="68">
@@ -2586,20 +2586,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9809</v>
+        <v>0.9748</v>
       </c>
       <c r="F68" t="n">
-        <v>1.9094</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0395</v>
+        <v>0.0446</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1074</v>
+        <v>0.1121</v>
       </c>
     </row>
     <row r="69">
@@ -2618,20 +2618,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9735</v>
+        <v>0.9673</v>
       </c>
       <c r="F69" t="n">
-        <v>1.8703</v>
+        <v>0.0316</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0424</v>
+        <v>0.0474</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1051</v>
+        <v>0.1142</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9735</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="F70" t="n">
-        <v>1.886</v>
+        <v>0.0318</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0386</v>
+        <v>0.0475</v>
       </c>
       <c r="H70" t="n">
-        <v>0.106</v>
+        <v>0.1142</v>
       </c>
     </row>
     <row r="71">
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9797</v>
+        <v>0.9789</v>
       </c>
       <c r="F71" t="n">
-        <v>1.8542</v>
+        <v>0.0373</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0416</v>
+        <v>0.0402</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1041</v>
+        <v>0.1138</v>
       </c>
     </row>
     <row r="72">
@@ -2714,20 +2714,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9676</v>
       </c>
       <c r="F72" t="n">
-        <v>1.8906</v>
+        <v>0.0392</v>
       </c>
       <c r="G72" t="n">
-        <v>0.042</v>
+        <v>0.0472</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1063</v>
+        <v>0.1137</v>
       </c>
     </row>
     <row r="73">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.972</v>
+        <v>0.9847</v>
       </c>
       <c r="F73" t="n">
-        <v>1.8561</v>
+        <v>0.0992</v>
       </c>
       <c r="G73" t="n">
-        <v>0.045</v>
+        <v>0.0412</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1042</v>
+        <v>0.1101</v>
       </c>
     </row>
     <row r="74">
@@ -2778,20 +2778,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9658</v>
+        <v>0.966</v>
       </c>
       <c r="F74" t="n">
-        <v>1.8163</v>
+        <v>0.1406</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0495</v>
+        <v>0.0503</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1018</v>
+        <v>0.1075</v>
       </c>
     </row>
     <row r="75">
@@ -2810,20 +2810,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9004</v>
+        <v>0.9746</v>
       </c>
       <c r="F75" t="n">
-        <v>1.9667</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0645</v>
+        <v>0.0415</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1107</v>
+        <v>0.1155</v>
       </c>
     </row>
     <row r="76">
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9004</v>
+        <v>0.9746</v>
       </c>
       <c r="F76" t="n">
-        <v>1.9667</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0645</v>
+        <v>0.0415</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1107</v>
+        <v>0.1155</v>
       </c>
     </row>
     <row r="77">
@@ -2874,20 +2874,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.8897</v>
       </c>
       <c r="F77" t="n">
-        <v>2.0165</v>
+        <v>-0.0115</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0735</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1135</v>
+        <v>0.1167</v>
       </c>
     </row>
     <row r="78">
@@ -2906,20 +2906,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8224</v>
+        <v>0.8757</v>
       </c>
       <c r="F78" t="n">
-        <v>2.0204</v>
+        <v>-0.0125</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0735</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1138</v>
+        <v>0.1167</v>
       </c>
     </row>
     <row r="79">
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8196</v>
+        <v>0.8772</v>
       </c>
       <c r="F79" t="n">
-        <v>2.0211</v>
+        <v>-0.0121</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0736</v>
+        <v>0.066</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1138</v>
+        <v>0.1167</v>
       </c>
     </row>
     <row r="80">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8226</v>
+        <v>0.8757</v>
       </c>
       <c r="F80" t="n">
-        <v>2.0211</v>
+        <v>-0.0127</v>
       </c>
       <c r="G80" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1138</v>
+        <v>0.1167</v>
       </c>
     </row>
     <row r="81">
@@ -3002,20 +3002,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.9741</v>
+        <v>0.9346</v>
       </c>
       <c r="F81" t="n">
-        <v>1.9221</v>
+        <v>0.0738</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0425</v>
+        <v>0.0577</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1081</v>
+        <v>0.1117</v>
       </c>
     </row>
     <row r="82">
@@ -3034,20 +3034,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.9712</v>
+        <v>0.9629</v>
       </c>
       <c r="F82" t="n">
-        <v>1.919</v>
+        <v>0.081</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0426</v>
+        <v>0.0483</v>
       </c>
       <c r="H82" t="n">
-        <v>0.108</v>
+        <v>0.1112</v>
       </c>
     </row>
     <row r="83">
@@ -3066,20 +3066,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.8912</v>
+        <v>0.9745</v>
       </c>
       <c r="F83" t="n">
-        <v>1.9653</v>
+        <v>0.0045</v>
       </c>
       <c r="G83" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0417</v>
       </c>
       <c r="H83" t="n">
-        <v>0.1106</v>
+        <v>0.1157</v>
       </c>
     </row>
     <row r="84">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.8923</v>
+        <v>0.9746</v>
       </c>
       <c r="F84" t="n">
-        <v>1.9644</v>
+        <v>0.0068</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0649</v>
+        <v>0.0417</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1106</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="85">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.8537</v>
+        <v>0.9746</v>
       </c>
       <c r="F85" t="n">
-        <v>1.9673</v>
+        <v>0.0027</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0723</v>
+        <v>0.0417</v>
       </c>
       <c r="H85" t="n">
-        <v>0.1108</v>
+        <v>0.1159</v>
       </c>
     </row>
     <row r="86">
@@ -3162,20 +3162,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9324</v>
+        <v>0.9741</v>
       </c>
       <c r="F86" t="n">
-        <v>1.9402</v>
+        <v>0.0058</v>
       </c>
       <c r="G86" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0482</v>
       </c>
       <c r="H86" t="n">
-        <v>0.1092</v>
+        <v>0.1157</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9791</v>
+        <v>0.9785</v>
       </c>
       <c r="F87" t="n">
-        <v>1.9294</v>
+        <v>0.0151</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0435</v>
+        <v>0.0412</v>
       </c>
       <c r="H87" t="n">
-        <v>0.1086</v>
+        <v>0.1151</v>
       </c>
     </row>
     <row r="88">
@@ -3226,20 +3226,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9609</v>
+        <v>0.9686</v>
       </c>
       <c r="F88" t="n">
-        <v>1.8784</v>
+        <v>0.0214</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0531</v>
+        <v>0.0489</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1056</v>
+        <v>0.1148</v>
       </c>
     </row>
     <row r="89">
@@ -3258,20 +3258,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.979</v>
+        <v>0.9728</v>
       </c>
       <c r="F89" t="n">
-        <v>1.8866</v>
+        <v>0.0157</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0425</v>
+        <v>0.0454</v>
       </c>
       <c r="H89" t="n">
-        <v>0.106</v>
+        <v>0.1151</v>
       </c>
     </row>
     <row r="90">
@@ -3290,20 +3290,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9823</v>
+        <v>0.9826</v>
       </c>
       <c r="F90" t="n">
-        <v>1.8035</v>
+        <v>0.1713</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0415</v>
+        <v>0.04</v>
       </c>
       <c r="H90" t="n">
-        <v>0.101</v>
+        <v>0.1056</v>
       </c>
     </row>
     <row r="91">
@@ -3322,20 +3322,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9804</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="F91" t="n">
-        <v>1.7416</v>
+        <v>0.1853</v>
       </c>
       <c r="G91" t="n">
-        <v>0.035</v>
+        <v>0.0393</v>
       </c>
       <c r="H91" t="n">
-        <v>0.097</v>
+        <v>0.1047</v>
       </c>
     </row>
     <row r="92">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9609</v>
+        <v>0.9686</v>
       </c>
       <c r="F92" t="n">
-        <v>1.8784</v>
+        <v>0.0214</v>
       </c>
       <c r="G92" t="n">
-        <v>0.053</v>
+        <v>0.0489</v>
       </c>
       <c r="H92" t="n">
-        <v>0.1056</v>
+        <v>0.1148</v>
       </c>
     </row>
     <row r="93">
@@ -3386,20 +3386,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9804</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="F93" t="n">
-        <v>1.7416</v>
+        <v>0.1853</v>
       </c>
       <c r="G93" t="n">
-        <v>0.035</v>
+        <v>0.0393</v>
       </c>
       <c r="H93" t="n">
-        <v>0.097</v>
+        <v>0.1047</v>
       </c>
     </row>
     <row r="94">
@@ -3418,20 +3418,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9012</v>
+        <v>0.9036</v>
       </c>
       <c r="F94" t="n">
-        <v>1.9911</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0614</v>
+        <v>0.0616</v>
       </c>
       <c r="H94" t="n">
-        <v>0.1121</v>
+        <v>0.1155</v>
       </c>
     </row>
     <row r="95">
@@ -3450,20 +3450,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.8193</v>
       </c>
       <c r="F95" t="n">
-        <v>2.1271</v>
+        <v>-0.0987</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0721</v>
+        <v>0.0774</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1196</v>
+        <v>0.1216</v>
       </c>
     </row>
     <row r="96">
@@ -3482,20 +3482,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.8954</v>
+        <v>0.8999</v>
       </c>
       <c r="F96" t="n">
-        <v>1.9942</v>
+        <v>-0.0013</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0626</v>
+        <v>0.063</v>
       </c>
       <c r="H96" t="n">
-        <v>0.1123</v>
+        <v>0.1161</v>
       </c>
     </row>
     <row r="97">
@@ -3514,20 +3514,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.8859</v>
+        <v>0.8993</v>
       </c>
       <c r="F97" t="n">
-        <v>1.994</v>
+        <v>0.0043</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0636</v>
+        <v>0.0631</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1123</v>
+        <v>0.1158</v>
       </c>
     </row>
     <row r="98">
@@ -3546,20 +3546,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9666</v>
       </c>
       <c r="F98" t="n">
-        <v>1.9473</v>
+        <v>0.0493</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0435</v>
+        <v>0.0538</v>
       </c>
       <c r="H98" t="n">
-        <v>0.1096</v>
+        <v>0.1131</v>
       </c>
     </row>
     <row r="99">
@@ -3578,20 +3578,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9443</v>
       </c>
       <c r="F99" t="n">
-        <v>1.942</v>
+        <v>-0.0047</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0436</v>
+        <v>0.0602</v>
       </c>
       <c r="H99" t="n">
-        <v>0.1093</v>
+        <v>0.1163</v>
       </c>
     </row>
     <row r="100">
@@ -3610,20 +3610,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9709</v>
+        <v>0.9362</v>
       </c>
       <c r="F100" t="n">
-        <v>1.9352</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0468</v>
+        <v>0.0601</v>
       </c>
       <c r="H100" t="n">
-        <v>0.1089</v>
+        <v>0.1154</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9755</v>
+        <v>0.9639</v>
       </c>
       <c r="F101" t="n">
-        <v>1.9259</v>
+        <v>-0.0043</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0409</v>
+        <v>0.0484</v>
       </c>
       <c r="H101" t="n">
-        <v>0.1084</v>
+        <v>0.1163</v>
       </c>
     </row>
     <row r="102">
@@ -3674,20 +3674,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.965</v>
+        <v>0.9614</v>
       </c>
       <c r="F102" t="n">
-        <v>1.9492</v>
+        <v>-0.0153</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0474</v>
+        <v>0.0508</v>
       </c>
       <c r="H102" t="n">
-        <v>0.1097</v>
+        <v>0.1169</v>
       </c>
     </row>
     <row r="103">
@@ -3706,20 +3706,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9823</v>
+        <v>0.988</v>
       </c>
       <c r="F103" t="n">
-        <v>1.9466</v>
+        <v>-0.0172</v>
       </c>
       <c r="G103" t="n">
-        <v>0.0473</v>
+        <v>0.0444</v>
       </c>
       <c r="H103" t="n">
-        <v>0.1096</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="104">
@@ -3738,20 +3738,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9835</v>
+        <v>0.9857</v>
       </c>
       <c r="F104" t="n">
-        <v>1.919</v>
+        <v>0.0383</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0399</v>
+        <v>0.0442</v>
       </c>
       <c r="H104" t="n">
-        <v>0.108</v>
+        <v>0.1138</v>
       </c>
     </row>
     <row r="105">
@@ -3774,16 +3774,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9818</v>
+        <v>0.9827</v>
       </c>
       <c r="F105" t="n">
-        <v>1.94</v>
+        <v>0.033</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0436</v>
+        <v>0.0435</v>
       </c>
       <c r="H105" t="n">
-        <v>0.1092</v>
+        <v>0.1141</v>
       </c>
     </row>
     <row r="106">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9754</v>
+        <v>0.9683</v>
       </c>
       <c r="F106" t="n">
-        <v>1.9435</v>
+        <v>-0.0137</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0466</v>
+        <v>0.0497</v>
       </c>
       <c r="H106" t="n">
-        <v>0.1094</v>
+        <v>0.1168</v>
       </c>
     </row>
     <row r="107">
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9444</v>
+        <v>0.9443</v>
       </c>
       <c r="F107" t="n">
-        <v>1.9375</v>
+        <v>-0.0007</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0564</v>
+        <v>0.0568</v>
       </c>
       <c r="H107" t="n">
-        <v>0.109</v>
+        <v>0.1161</v>
       </c>
     </row>
     <row r="108">
@@ -3866,20 +3866,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9807</v>
       </c>
       <c r="F108" t="n">
-        <v>1.8387</v>
+        <v>0.1137</v>
       </c>
       <c r="G108" t="n">
-        <v>0.0404</v>
+        <v>0.0501</v>
       </c>
       <c r="H108" t="n">
-        <v>0.1031</v>
+        <v>0.1092</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9858</v>
+        <v>0.9872</v>
       </c>
       <c r="F109" t="n">
-        <v>1.8199</v>
+        <v>0.1435</v>
       </c>
       <c r="G109" t="n">
-        <v>0.0425</v>
+        <v>0.0408</v>
       </c>
       <c r="H109" t="n">
-        <v>0.102</v>
+        <v>0.1074</v>
       </c>
     </row>
     <row r="110">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9781</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="F110" t="n">
-        <v>1.7599</v>
+        <v>0.1803</v>
       </c>
       <c r="G110" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0982</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="111">
@@ -3962,20 +3962,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9833</v>
+        <v>0.9821</v>
       </c>
       <c r="F111" t="n">
-        <v>1.7303</v>
+        <v>0.2168</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0361</v>
+        <v>0.0364</v>
       </c>
       <c r="H111" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.1027</v>
       </c>
     </row>
     <row r="112">
@@ -3998,16 +3998,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9811</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="F112" t="n">
-        <v>1.8353</v>
+        <v>0.1121</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0447</v>
+        <v>0.0458</v>
       </c>
       <c r="H112" t="n">
-        <v>0.1029</v>
+        <v>0.1093</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9801</v>
       </c>
       <c r="F113" t="n">
-        <v>1.815</v>
+        <v>0.1422</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0544</v>
+        <v>0.0488</v>
       </c>
       <c r="H113" t="n">
-        <v>0.1017</v>
+        <v>0.1074</v>
       </c>
     </row>
     <row r="114">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9794</v>
+        <v>0.9843</v>
       </c>
       <c r="F114" t="n">
-        <v>1.7476</v>
+        <v>0.1843</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0393</v>
+        <v>0.0392</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0974</v>
+        <v>0.1048</v>
       </c>
     </row>
     <row r="115">
@@ -4090,20 +4090,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9841</v>
+        <v>0.9818</v>
       </c>
       <c r="F115" t="n">
-        <v>1.7305</v>
+        <v>0.2113</v>
       </c>
       <c r="G115" t="n">
-        <v>0.036</v>
+        <v>0.0367</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0963</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="116">
@@ -4122,20 +4122,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9702</v>
       </c>
       <c r="F116" t="n">
-        <v>1.9255</v>
+        <v>0.0504</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0409</v>
+        <v>0.0455</v>
       </c>
       <c r="H116" t="n">
-        <v>0.1083</v>
+        <v>0.1131</v>
       </c>
     </row>
     <row r="117">
@@ -4154,20 +4154,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.928</v>
+        <v>0.9691</v>
       </c>
       <c r="F117" t="n">
-        <v>1.9446</v>
+        <v>0.0519</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0577</v>
+        <v>0.0434</v>
       </c>
       <c r="H117" t="n">
-        <v>0.1095</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="118">
@@ -4190,16 +4190,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9818</v>
+        <v>0.9827</v>
       </c>
       <c r="F118" t="n">
-        <v>1.94</v>
+        <v>0.033</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0436</v>
+        <v>0.0435</v>
       </c>
       <c r="H118" t="n">
-        <v>0.1092</v>
+        <v>0.1141</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9801</v>
       </c>
       <c r="F119" t="n">
-        <v>1.815</v>
+        <v>0.1422</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0544</v>
+        <v>0.0488</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1017</v>
+        <v>0.1074</v>
       </c>
     </row>
     <row r="120">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9297</v>
+        <v>0.9701</v>
       </c>
       <c r="F120" t="n">
-        <v>2.0037</v>
+        <v>-0.041</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0617</v>
+        <v>0.048</v>
       </c>
       <c r="H120" t="n">
-        <v>0.1128</v>
+        <v>0.1184</v>
       </c>
     </row>
     <row r="121">
@@ -4282,20 +4282,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9297</v>
+        <v>0.9701</v>
       </c>
       <c r="F121" t="n">
-        <v>2.0037</v>
+        <v>-0.041</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0617</v>
+        <v>0.048</v>
       </c>
       <c r="H121" t="n">
-        <v>0.1128</v>
+        <v>0.1184</v>
       </c>
     </row>
     <row r="122">
@@ -4314,20 +4314,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9784</v>
+        <v>0.9831</v>
       </c>
       <c r="F122" t="n">
-        <v>1.9604</v>
+        <v>-0.0173</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0424</v>
+        <v>0.0413</v>
       </c>
       <c r="H122" t="n">
-        <v>0.1104</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9826</v>
+        <v>0.9802</v>
       </c>
       <c r="F123" t="n">
-        <v>1.8139</v>
+        <v>0.1425</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0382</v>
+        <v>0.0488</v>
       </c>
       <c r="H123" t="n">
-        <v>0.1016</v>
+        <v>0.1074</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9777</v>
+        <v>0.9852</v>
       </c>
       <c r="F124" t="n">
-        <v>1.7733</v>
+        <v>0.1614</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0398</v>
+        <v>0.043</v>
       </c>
       <c r="H124" t="n">
-        <v>0.099</v>
+        <v>0.1062</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9021</v>
+        <v>0.9028</v>
       </c>
       <c r="F125" t="n">
-        <v>1.9873</v>
+        <v>0.0125</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0612</v>
+        <v>0.0624</v>
       </c>
       <c r="H125" t="n">
-        <v>0.1119</v>
+        <v>0.1153</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9686</v>
+        <v>0.9639</v>
       </c>
       <c r="F126" t="n">
-        <v>1.9389</v>
+        <v>-0.0196</v>
       </c>
       <c r="G126" t="n">
-        <v>0.047</v>
+        <v>0.0486</v>
       </c>
       <c r="H126" t="n">
-        <v>0.1091</v>
+        <v>0.1171</v>
       </c>
     </row>
     <row r="127">
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.8939</v>
+        <v>0.8832</v>
       </c>
       <c r="F127" t="n">
-        <v>2.0079</v>
+        <v>0.0054</v>
       </c>
       <c r="G127" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0635</v>
       </c>
       <c r="H127" t="n">
-        <v>0.1131</v>
+        <v>0.1157</v>
       </c>
     </row>
     <row r="128">
@@ -4506,20 +4506,20 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.959</v>
+        <v>0.9666</v>
       </c>
       <c r="F128" t="n">
-        <v>1.9112</v>
+        <v>0.0042</v>
       </c>
       <c r="G128" t="n">
-        <v>0.0469</v>
+        <v>0.0463</v>
       </c>
       <c r="H128" t="n">
-        <v>0.1075</v>
+        <v>0.1158</v>
       </c>
     </row>
     <row r="129">
@@ -4542,16 +4542,16 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9649</v>
       </c>
       <c r="F129" t="n">
-        <v>1.9216</v>
+        <v>0.0098</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0442</v>
+        <v>0.0464</v>
       </c>
       <c r="H129" t="n">
-        <v>0.1081</v>
+        <v>0.1154</v>
       </c>
     </row>
     <row r="130">
@@ -4570,20 +4570,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.9665</v>
+        <v>0.9656</v>
       </c>
       <c r="F130" t="n">
-        <v>1.9283</v>
+        <v>-0.0039</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0471</v>
+        <v>0.0468</v>
       </c>
       <c r="H130" t="n">
-        <v>0.1085</v>
+        <v>0.1162</v>
       </c>
     </row>
     <row r="131">
@@ -4602,20 +4602,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.9668</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>1.9289</v>
+        <v>-0.0201</v>
       </c>
       <c r="G131" t="n">
-        <v>0.0467</v>
+        <v>0.0605</v>
       </c>
       <c r="H131" t="n">
-        <v>0.1085</v>
+        <v>0.1172</v>
       </c>
     </row>
     <row r="132">
@@ -4634,20 +4634,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.9585</v>
+        <v>0.9706</v>
       </c>
       <c r="F132" t="n">
-        <v>1.9202</v>
+        <v>-0.0242</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0478</v>
+        <v>0.046</v>
       </c>
       <c r="H132" t="n">
-        <v>0.108</v>
+        <v>0.1174</v>
       </c>
     </row>
     <row r="133">
@@ -4666,20 +4666,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.9712</v>
       </c>
       <c r="F133" t="n">
-        <v>1.9213</v>
+        <v>-0.0136</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0447</v>
+        <v>0.0459</v>
       </c>
       <c r="H133" t="n">
-        <v>0.1081</v>
+        <v>0.1168</v>
       </c>
     </row>
     <row r="134">
@@ -4698,20 +4698,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.966</v>
+        <v>0.9707</v>
       </c>
       <c r="F134" t="n">
-        <v>1.9224</v>
+        <v>-0.0319</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0469</v>
+        <v>0.0465</v>
       </c>
       <c r="H134" t="n">
-        <v>0.1082</v>
+        <v>0.1178</v>
       </c>
     </row>
     <row r="135">
@@ -4730,20 +4730,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.9552</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="F135" t="n">
-        <v>1.9196</v>
+        <v>-0.0125</v>
       </c>
       <c r="G135" t="n">
-        <v>0.05</v>
+        <v>0.0468</v>
       </c>
       <c r="H135" t="n">
-        <v>0.108</v>
+        <v>0.1167</v>
       </c>
     </row>
     <row r="136">
@@ -4762,20 +4762,20 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.9666</v>
+        <v>0.9679</v>
       </c>
       <c r="F136" t="n">
-        <v>1.932</v>
+        <v>-0.0135</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0464</v>
+        <v>0.0467</v>
       </c>
       <c r="H136" t="n">
-        <v>0.1087</v>
+        <v>0.1168</v>
       </c>
     </row>
     <row r="137">
@@ -4798,16 +4798,16 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9821</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="F137" t="n">
-        <v>1.9324</v>
+        <v>0.0352</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0436</v>
+        <v>0.0441</v>
       </c>
       <c r="H137" t="n">
-        <v>0.1087</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="138">
@@ -4826,20 +4826,20 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9621</v>
+        <v>0.9817</v>
       </c>
       <c r="F138" t="n">
-        <v>1.9369</v>
+        <v>0.0141</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0539</v>
+        <v>0.0452</v>
       </c>
       <c r="H138" t="n">
-        <v>0.109</v>
+        <v>0.1152</v>
       </c>
     </row>
     <row r="139">
@@ -4858,20 +4858,20 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9833</v>
+        <v>0.9614</v>
       </c>
       <c r="F139" t="n">
-        <v>1.9671</v>
+        <v>-0.0467</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0442</v>
+        <v>0.0576</v>
       </c>
       <c r="H139" t="n">
-        <v>0.1108</v>
+        <v>0.1187</v>
       </c>
     </row>
     <row r="140">
@@ -4890,20 +4890,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.9879</v>
+        <v>0.9841</v>
       </c>
       <c r="F140" t="n">
-        <v>1.8424</v>
+        <v>0.1111</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0386</v>
+        <v>0.0435</v>
       </c>
       <c r="H140" t="n">
-        <v>0.1034</v>
+        <v>0.1094</v>
       </c>
     </row>
     <row r="141">
@@ -4922,20 +4922,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9869</v>
+        <v>0.9906</v>
       </c>
       <c r="F141" t="n">
-        <v>1.8058</v>
+        <v>0.1204</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0359</v>
+        <v>0.0376</v>
       </c>
       <c r="H141" t="n">
-        <v>0.1011</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="142">
@@ -4954,20 +4954,20 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9621</v>
+        <v>0.9817</v>
       </c>
       <c r="F142" t="n">
-        <v>1.9369</v>
+        <v>0.0141</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0539</v>
+        <v>0.0452</v>
       </c>
       <c r="H142" t="n">
-        <v>0.109</v>
+        <v>0.1152</v>
       </c>
     </row>
     <row r="143">
@@ -4986,20 +4986,20 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.9648</v>
+        <v>0.9848</v>
       </c>
       <c r="F143" t="n">
-        <v>2.0105</v>
+        <v>-0.04</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0573</v>
+        <v>0.0459</v>
       </c>
       <c r="H143" t="n">
-        <v>0.1132</v>
+        <v>0.1183</v>
       </c>
     </row>
     <row r="144">
@@ -5018,20 +5018,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9606</v>
+        <v>0.9796</v>
       </c>
       <c r="F144" t="n">
-        <v>1.9918</v>
+        <v>-0.0357</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0579</v>
+        <v>0.0437</v>
       </c>
       <c r="H144" t="n">
-        <v>0.1122</v>
+        <v>0.1181</v>
       </c>
     </row>
     <row r="145">
@@ -5050,20 +5050,20 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9869</v>
+        <v>0.9906</v>
       </c>
       <c r="F145" t="n">
-        <v>1.8058</v>
+        <v>0.1204</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0359</v>
+        <v>0.0376</v>
       </c>
       <c r="H145" t="n">
-        <v>0.1011</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="146">
@@ -5082,20 +5082,20 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.8943</v>
+        <v>0.8847</v>
       </c>
       <c r="F146" t="n">
-        <v>2.0182</v>
+        <v>0.0133</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0624</v>
+        <v>0.0633</v>
       </c>
       <c r="H146" t="n">
-        <v>0.1136</v>
+        <v>0.1152</v>
       </c>
     </row>
     <row r="147">
@@ -5114,20 +5114,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.8932</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="F147" t="n">
-        <v>2.0149</v>
+        <v>0.0186</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0626</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="H147" t="n">
-        <v>0.1135</v>
+        <v>0.1149</v>
       </c>
     </row>
     <row r="148">
@@ -5146,20 +5146,20 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.8884</v>
+        <v>0.8825</v>
       </c>
       <c r="F148" t="n">
-        <v>2.0165</v>
+        <v>0.015</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0629</v>
+        <v>0.0633</v>
       </c>
       <c r="H148" t="n">
-        <v>0.1136</v>
+        <v>0.1151</v>
       </c>
     </row>
     <row r="149">
@@ -5178,20 +5178,20 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.8892</v>
+        <v>0.8935999999999999</v>
       </c>
       <c r="F149" t="n">
-        <v>2.0215</v>
+        <v>0.0058</v>
       </c>
       <c r="G149" t="n">
-        <v>0.063</v>
+        <v>0.0614</v>
       </c>
       <c r="H149" t="n">
-        <v>0.1138</v>
+        <v>0.1157</v>
       </c>
     </row>
     <row r="150">
@@ -5210,20 +5210,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.8917</v>
+        <v>0.8825</v>
       </c>
       <c r="F150" t="n">
-        <v>2.0088</v>
+        <v>0.0078</v>
       </c>
       <c r="G150" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0636</v>
       </c>
       <c r="H150" t="n">
-        <v>0.1131</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="151">
@@ -5242,20 +5242,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.8923</v>
+        <v>0.8828</v>
       </c>
       <c r="F151" t="n">
-        <v>2.017</v>
+        <v>0.0094</v>
       </c>
       <c r="G151" t="n">
-        <v>0.063</v>
+        <v>0.0636</v>
       </c>
       <c r="H151" t="n">
-        <v>0.1136</v>
+        <v>0.1155</v>
       </c>
     </row>
     <row r="152">
@@ -5274,20 +5274,20 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.8929</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="F152" t="n">
-        <v>2.0204</v>
+        <v>0.0063</v>
       </c>
       <c r="G152" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0635</v>
       </c>
       <c r="H152" t="n">
-        <v>0.1138</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="153">
@@ -5306,20 +5306,20 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.8778</v>
+        <v>0.8819</v>
       </c>
       <c r="F153" t="n">
-        <v>2.0237</v>
+        <v>0.0061</v>
       </c>
       <c r="G153" t="n">
-        <v>0.0665</v>
+        <v>0.0636</v>
       </c>
       <c r="H153" t="n">
-        <v>0.114</v>
+        <v>0.1157</v>
       </c>
     </row>
     <row r="154">
@@ -5338,20 +5338,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.8919</v>
+        <v>0.8941</v>
       </c>
       <c r="F154" t="n">
-        <v>2.0238</v>
+        <v>0.0124</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0629</v>
+        <v>0.0613</v>
       </c>
       <c r="H154" t="n">
-        <v>0.114</v>
+        <v>0.1153</v>
       </c>
     </row>
     <row r="155">
@@ -5370,20 +5370,20 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9135</v>
       </c>
       <c r="F155" t="n">
-        <v>1.9373</v>
+        <v>0.0109</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0569</v>
+        <v>0.0633</v>
       </c>
       <c r="H155" t="n">
-        <v>0.109</v>
+        <v>0.1154</v>
       </c>
     </row>
     <row r="156">
@@ -5402,20 +5402,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.9584</v>
+        <v>0.9064</v>
       </c>
       <c r="F156" t="n">
-        <v>1.9664</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0471</v>
+        <v>0.0636</v>
       </c>
       <c r="H156" t="n">
-        <v>0.1107</v>
+        <v>0.1155</v>
       </c>
     </row>
     <row r="157">
@@ -5438,16 +5438,16 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.9204</v>
+        <v>0.9101</v>
       </c>
       <c r="F157" t="n">
-        <v>1.9756</v>
+        <v>0.0238</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0595</v>
+        <v>0.0612</v>
       </c>
       <c r="H157" t="n">
-        <v>0.1112</v>
+        <v>0.1146</v>
       </c>
     </row>
     <row r="158">
@@ -5466,20 +5466,20 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.9565</v>
+        <v>0.9215</v>
       </c>
       <c r="F158" t="n">
-        <v>1.9997</v>
+        <v>-0.0122</v>
       </c>
       <c r="G158" t="n">
-        <v>0.0537</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="H158" t="n">
-        <v>0.1126</v>
+        <v>0.1167</v>
       </c>
     </row>
     <row r="159">
@@ -5498,20 +5498,20 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.9115</v>
+        <v>0.9787</v>
       </c>
       <c r="F159" t="n">
-        <v>1.9695</v>
+        <v>-0.0537</v>
       </c>
       <c r="G159" t="n">
-        <v>0.063</v>
+        <v>0.042</v>
       </c>
       <c r="H159" t="n">
-        <v>0.1109</v>
+        <v>0.1191</v>
       </c>
     </row>
     <row r="160">
@@ -5534,16 +5534,16 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.8216</v>
+        <v>0.8182</v>
       </c>
       <c r="F160" t="n">
-        <v>2.0554</v>
+        <v>-0.0427</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0751</v>
+        <v>0.0766</v>
       </c>
       <c r="H160" t="n">
-        <v>0.1157</v>
+        <v>0.1185</v>
       </c>
     </row>
     <row r="161">
@@ -5562,20 +5562,20 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.8659</v>
+        <v>0.8179</v>
       </c>
       <c r="F161" t="n">
-        <v>2.0486</v>
+        <v>-0.0412</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0687</v>
+        <v>0.0767</v>
       </c>
       <c r="H161" t="n">
-        <v>0.1153</v>
+        <v>0.1184</v>
       </c>
     </row>
     <row r="162">
@@ -5594,20 +5594,20 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.9655</v>
+        <v>0.9746</v>
       </c>
       <c r="F162" t="n">
-        <v>1.9808</v>
+        <v>-0.0498</v>
       </c>
       <c r="G162" t="n">
-        <v>0.0491</v>
+        <v>0.0439</v>
       </c>
       <c r="H162" t="n">
-        <v>0.1115</v>
+        <v>0.1189</v>
       </c>
     </row>
     <row r="163">
@@ -5626,20 +5626,20 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9818</v>
+        <v>0.9849</v>
       </c>
       <c r="F163" t="n">
-        <v>1.9181</v>
+        <v>-0.0171</v>
       </c>
       <c r="G163" t="n">
-        <v>0.0431</v>
+        <v>0.0442</v>
       </c>
       <c r="H163" t="n">
-        <v>0.1079</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="164">
@@ -5658,20 +5658,20 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.9881</v>
+        <v>0.9841</v>
       </c>
       <c r="F164" t="n">
-        <v>1.8428</v>
+        <v>0.1109</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0386</v>
+        <v>0.0435</v>
       </c>
       <c r="H164" t="n">
-        <v>0.1034</v>
+        <v>0.1094</v>
       </c>
     </row>
     <row r="165">
@@ -5690,20 +5690,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9021</v>
+        <v>0.9028</v>
       </c>
       <c r="F165" t="n">
-        <v>1.9873</v>
+        <v>0.0125</v>
       </c>
       <c r="G165" t="n">
-        <v>0.0612</v>
+        <v>0.0624</v>
       </c>
       <c r="H165" t="n">
-        <v>0.1119</v>
+        <v>0.1153</v>
       </c>
     </row>
     <row r="166">
@@ -5726,16 +5726,16 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.8536</v>
+        <v>0.8526</v>
       </c>
       <c r="F166" t="n">
-        <v>2.1281</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="G166" t="n">
-        <v>0.0727</v>
+        <v>0.074</v>
       </c>
       <c r="H166" t="n">
-        <v>0.1196</v>
+        <v>0.1217</v>
       </c>
     </row>
     <row r="167">
@@ -5754,20 +5754,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.9641</v>
+        <v>0.9295</v>
       </c>
       <c r="F167" t="n">
-        <v>1.8484</v>
+        <v>0.0675</v>
       </c>
       <c r="G167" t="n">
-        <v>0.0512</v>
+        <v>0.0623</v>
       </c>
       <c r="H167" t="n">
-        <v>0.1037</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="168">
@@ -5786,20 +5786,20 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9846</v>
+        <v>0.9812</v>
       </c>
       <c r="F168" t="n">
-        <v>1.831</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0385</v>
+        <v>0.0453</v>
       </c>
       <c r="H168" t="n">
-        <v>0.1027</v>
+        <v>0.1101</v>
       </c>
     </row>
     <row r="169">
@@ -5818,20 +5818,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.98</v>
+        <v>0.9828</v>
       </c>
       <c r="F169" t="n">
-        <v>1.8122</v>
+        <v>0.1622</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0394</v>
+        <v>0.0373</v>
       </c>
       <c r="H169" t="n">
-        <v>0.1015</v>
+        <v>0.1062</v>
       </c>
     </row>
     <row r="170">
@@ -5850,20 +5850,20 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.982</v>
+        <v>0.9851</v>
       </c>
       <c r="F170" t="n">
-        <v>1.8188</v>
+        <v>0.1231</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0382</v>
+        <v>0.0412</v>
       </c>
       <c r="H170" t="n">
-        <v>0.1019</v>
+        <v>0.1086</v>
       </c>
     </row>
     <row r="171">
@@ -5882,20 +5882,20 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9815</v>
+        <v>0.9847</v>
       </c>
       <c r="F171" t="n">
-        <v>1.7716</v>
+        <v>0.1789</v>
       </c>
       <c r="G171" t="n">
-        <v>0.0382</v>
+        <v>0.0371</v>
       </c>
       <c r="H171" t="n">
-        <v>0.0989</v>
+        <v>0.1051</v>
       </c>
     </row>
     <row r="172">
@@ -5914,20 +5914,20 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9338</v>
+        <v>0.9741</v>
       </c>
       <c r="F172" t="n">
-        <v>2.0017</v>
+        <v>-0.1251</v>
       </c>
       <c r="G172" t="n">
-        <v>0.062</v>
+        <v>0.0493</v>
       </c>
       <c r="H172" t="n">
-        <v>0.1127</v>
+        <v>0.1231</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/ratio.alpha.natif/RANDOMSEARCH_DETAILS_ratio.alpha.natif.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/ratio.alpha.natif/RANDOMSEARCH_DETAILS_ratio.alpha.natif.xlsx
@@ -922,7 +922,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E108" t="n">
